--- a/TFG_MODELOS_SIMPLES2/02_datasets/metadata/METADATA.xlsx
+++ b/TFG_MODELOS_SIMPLES2/02_datasets/metadata/METADATA.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Scripts-CIC18" sheetId="1" state="visible" r:id="rId3"/>
@@ -3296,7 +3296,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="112">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3523,10 +3523,6 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -3827,14 +3823,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>23760</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1013040</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>160560</xdr:rowOff>
+      <xdr:colOff>1012680</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>183600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3848,7 +3844,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="19857240"/>
-          <a:ext cx="3866040" cy="3441960"/>
+          <a:ext cx="3865680" cy="3441600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3864,14 +3860,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>23760</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>141120</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>160560</xdr:rowOff>
+      <xdr:colOff>140760</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>183600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3885,7 +3881,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6363360" y="19857240"/>
-          <a:ext cx="3866040" cy="3441960"/>
+          <a:ext cx="3865680" cy="3441600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3901,14 +3897,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>23760</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>169560</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>160560</xdr:rowOff>
+      <xdr:colOff>169200</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>183600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3922,7 +3918,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11784240" y="19857240"/>
-          <a:ext cx="3866040" cy="3441960"/>
+          <a:ext cx="3865680" cy="3441600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3938,14 +3934,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>23760</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>620640</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>160560</xdr:rowOff>
+      <xdr:colOff>620280</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>183600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3959,7 +3955,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16963560" y="19857240"/>
-          <a:ext cx="3866040" cy="3441960"/>
+          <a:ext cx="3865680" cy="3441600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3975,14 +3971,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>23400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1013040</xdr:colOff>
-      <xdr:row>117</xdr:row>
-      <xdr:rowOff>160200</xdr:rowOff>
+      <xdr:colOff>1012680</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>183600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3996,7 +3992,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="24369480"/>
-          <a:ext cx="3866040" cy="3441960"/>
+          <a:ext cx="3865680" cy="3441600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4022,9 +4018,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1930320</xdr:colOff>
+      <xdr:colOff>1929960</xdr:colOff>
       <xdr:row>94</xdr:row>
-      <xdr:rowOff>34920</xdr:rowOff>
+      <xdr:rowOff>34200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4037,8 +4033,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="20103480"/>
-          <a:ext cx="4283640" cy="3498120"/>
+          <a:off x="0" y="19827000"/>
+          <a:ext cx="4283280" cy="3497760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4059,9 +4055,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>840960</xdr:colOff>
+      <xdr:colOff>840600</xdr:colOff>
       <xdr:row>94</xdr:row>
-      <xdr:rowOff>34920</xdr:rowOff>
+      <xdr:rowOff>34200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4074,8 +4070,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5987880" y="20103480"/>
-          <a:ext cx="4283640" cy="3498120"/>
+          <a:off x="5987880" y="19827000"/>
+          <a:ext cx="4283280" cy="3497760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4096,9 +4092,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1159200</xdr:colOff>
+      <xdr:colOff>1158840</xdr:colOff>
       <xdr:row>94</xdr:row>
-      <xdr:rowOff>34920</xdr:rowOff>
+      <xdr:rowOff>34200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4111,8 +4107,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11009520" y="20103480"/>
-          <a:ext cx="4283640" cy="3498120"/>
+          <a:off x="11009520" y="19827000"/>
+          <a:ext cx="4283280" cy="3497760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4133,9 +4129,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>1198800</xdr:colOff>
+      <xdr:colOff>1198440</xdr:colOff>
       <xdr:row>94</xdr:row>
-      <xdr:rowOff>34920</xdr:rowOff>
+      <xdr:rowOff>34200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4148,8 +4144,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15857280" y="20103480"/>
-          <a:ext cx="4283640" cy="3498120"/>
+          <a:off x="15857280" y="19827000"/>
+          <a:ext cx="4283280" cy="3497760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4170,9 +4166,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>210240</xdr:colOff>
+      <xdr:colOff>209880</xdr:colOff>
       <xdr:row>94</xdr:row>
-      <xdr:rowOff>34920</xdr:rowOff>
+      <xdr:rowOff>34200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4185,8 +4181,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20526480" y="20103480"/>
-          <a:ext cx="4283640" cy="3498120"/>
+          <a:off x="20526480" y="19827000"/>
+          <a:ext cx="4283280" cy="3497760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4208,13 +4204,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>191160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1572480</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>19080</xdr:rowOff>
+      <xdr:colOff>1572120</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>4680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4228,7 +4224,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="21096720"/>
-          <a:ext cx="3862800" cy="3435120"/>
+          <a:ext cx="3862440" cy="3434760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4245,13 +4241,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>191160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>978840</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>19080</xdr:rowOff>
+      <xdr:colOff>978480</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>4680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4265,7 +4261,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5584320" y="21096720"/>
-          <a:ext cx="3862800" cy="3435120"/>
+          <a:ext cx="3862440" cy="3434760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4282,13 +4278,13 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>191160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>944280</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>19080</xdr:rowOff>
+      <xdr:colOff>943920</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>4680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4302,7 +4298,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9972000" y="21096720"/>
-          <a:ext cx="3862800" cy="3435120"/>
+          <a:ext cx="3862440" cy="3434760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4319,13 +4315,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>93</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>191160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1572480</xdr:colOff>
-      <xdr:row>109</xdr:row>
-      <xdr:rowOff>153720</xdr:rowOff>
+      <xdr:colOff>1572120</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>139320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4339,7 +4335,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="25128360"/>
-          <a:ext cx="3862800" cy="3435120"/>
+          <a:ext cx="3862440" cy="3434760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4356,13 +4352,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>93</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>191160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>978840</xdr:colOff>
-      <xdr:row>109</xdr:row>
-      <xdr:rowOff>153720</xdr:rowOff>
+      <xdr:colOff>978480</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>139320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4376,7 +4372,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5584320" y="25128360"/>
-          <a:ext cx="3862800" cy="3435120"/>
+          <a:ext cx="3862440" cy="3434760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5947,7 +5943,7 @@
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G23" s="35"/>
     </row>
-    <row r="24" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="54" t="s">
         <v>91</v>
       </c>
@@ -5982,666 +5978,666 @@
         <v>101</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="56" t="n">
         <v>1</v>
       </c>
       <c r="B25" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="57" t="s">
+      <c r="C25" s="42" t="s">
         <v>103</v>
       </c>
-      <c r="D25" s="57" t="s">
+      <c r="D25" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="E25" s="57" t="s">
+      <c r="E25" s="42" t="s">
         <v>103</v>
       </c>
-      <c r="F25" s="57" t="s">
+      <c r="F25" s="42" t="s">
         <v>105</v>
       </c>
-      <c r="G25" s="57" t="s">
+      <c r="G25" s="42" t="s">
         <v>106</v>
       </c>
-      <c r="H25" s="57" t="s">
+      <c r="H25" s="42" t="s">
         <v>107</v>
       </c>
-      <c r="I25" s="57" t="s">
+      <c r="I25" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="J25" s="57" t="s">
+      <c r="J25" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="K25" s="57" t="s">
+      <c r="K25" s="42" t="s">
         <v>110</v>
       </c>
       <c r="L25" s="35"/>
     </row>
-    <row r="26" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="56" t="n">
         <v>2</v>
       </c>
       <c r="B26" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="C26" s="57" t="s">
+      <c r="C26" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="D26" s="57" t="s">
+      <c r="D26" s="42" t="s">
         <v>113</v>
       </c>
-      <c r="E26" s="57" t="s">
+      <c r="E26" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="F26" s="57" t="s">
+      <c r="F26" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="G26" s="57" t="s">
+      <c r="G26" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="H26" s="57" t="s">
+      <c r="H26" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="I26" s="57" t="s">
+      <c r="I26" s="42" t="s">
         <v>117</v>
       </c>
-      <c r="J26" s="57" t="s">
+      <c r="J26" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="K26" s="57" t="s">
+      <c r="K26" s="42" t="s">
         <v>119</v>
       </c>
       <c r="L26" s="35"/>
     </row>
-    <row r="27" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B27" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="C27" s="57" t="s">
+      <c r="C27" s="42" t="s">
         <v>121</v>
       </c>
-      <c r="D27" s="57" t="s">
+      <c r="D27" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="E27" s="57" t="s">
+      <c r="E27" s="42" t="s">
         <v>121</v>
       </c>
-      <c r="F27" s="57" t="s">
+      <c r="F27" s="42" t="s">
         <v>123</v>
       </c>
-      <c r="G27" s="57" t="s">
+      <c r="G27" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="H27" s="57" t="s">
+      <c r="H27" s="42" t="s">
         <v>125</v>
       </c>
-      <c r="I27" s="57" t="s">
+      <c r="I27" s="42" t="s">
         <v>126</v>
       </c>
-      <c r="J27" s="57" t="s">
+      <c r="J27" s="42" t="s">
         <v>127</v>
       </c>
-      <c r="K27" s="57" t="s">
+      <c r="K27" s="42" t="s">
         <v>128</v>
       </c>
       <c r="L27" s="35"/>
     </row>
-    <row r="28" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B28" s="56" t="s">
         <v>129</v>
       </c>
-      <c r="C28" s="57" t="s">
+      <c r="C28" s="42" t="s">
         <v>130</v>
       </c>
-      <c r="D28" s="57" t="s">
+      <c r="D28" s="42" t="s">
         <v>131</v>
       </c>
-      <c r="E28" s="57" t="s">
+      <c r="E28" s="42" t="s">
         <v>132</v>
       </c>
-      <c r="F28" s="57" t="s">
+      <c r="F28" s="42" t="s">
         <v>133</v>
       </c>
-      <c r="G28" s="57" t="s">
+      <c r="G28" s="42" t="s">
         <v>131</v>
       </c>
-      <c r="H28" s="57" t="s">
+      <c r="H28" s="42" t="s">
         <v>130</v>
       </c>
-      <c r="I28" s="57" t="s">
+      <c r="I28" s="42" t="s">
         <v>133</v>
       </c>
-      <c r="J28" s="57" t="s">
+      <c r="J28" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="K28" s="57" t="s">
+      <c r="K28" s="42" t="s">
         <v>135</v>
       </c>
       <c r="L28" s="35"/>
     </row>
-    <row r="29" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B29" s="56" t="s">
         <v>136</v>
       </c>
-      <c r="C29" s="57" t="s">
+      <c r="C29" s="42" t="s">
         <v>137</v>
       </c>
-      <c r="D29" s="57" t="s">
+      <c r="D29" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="E29" s="57" t="s">
+      <c r="E29" s="42" t="s">
         <v>137</v>
       </c>
-      <c r="F29" s="57" t="s">
+      <c r="F29" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="G29" s="57" t="s">
+      <c r="G29" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="H29" s="57" t="s">
+      <c r="H29" s="42" t="s">
         <v>137</v>
       </c>
-      <c r="I29" s="57" t="s">
+      <c r="I29" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="J29" s="57" t="s">
+      <c r="J29" s="42" t="s">
         <v>140</v>
       </c>
-      <c r="K29" s="57" t="s">
+      <c r="K29" s="42" t="s">
         <v>141</v>
       </c>
       <c r="L29" s="35"/>
     </row>
-    <row r="30" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="56" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B30" s="56" t="s">
         <v>142</v>
       </c>
-      <c r="C30" s="57" t="s">
+      <c r="C30" s="42" t="s">
         <v>143</v>
       </c>
-      <c r="D30" s="57" t="s">
+      <c r="D30" s="42" t="s">
         <v>144</v>
       </c>
-      <c r="E30" s="57" t="s">
+      <c r="E30" s="42" t="s">
         <v>143</v>
       </c>
-      <c r="F30" s="57" t="s">
+      <c r="F30" s="42" t="s">
         <v>145</v>
       </c>
-      <c r="G30" s="57" t="s">
+      <c r="G30" s="42" t="s">
         <v>144</v>
       </c>
-      <c r="H30" s="57" t="s">
+      <c r="H30" s="42" t="s">
         <v>143</v>
       </c>
-      <c r="I30" s="57" t="s">
+      <c r="I30" s="42" t="s">
         <v>145</v>
       </c>
-      <c r="J30" s="57" t="s">
+      <c r="J30" s="42" t="s">
         <v>146</v>
       </c>
-      <c r="K30" s="57" t="s">
+      <c r="K30" s="42" t="s">
         <v>147</v>
       </c>
       <c r="L30" s="35"/>
     </row>
-    <row r="31" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="56" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B31" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="C31" s="57" t="s">
+      <c r="C31" s="42" t="s">
         <v>149</v>
       </c>
-      <c r="D31" s="57" t="s">
+      <c r="D31" s="42" t="s">
         <v>150</v>
       </c>
-      <c r="E31" s="57" t="s">
+      <c r="E31" s="42" t="s">
         <v>149</v>
       </c>
-      <c r="F31" s="57" t="s">
+      <c r="F31" s="42" t="s">
         <v>151</v>
       </c>
-      <c r="G31" s="57" t="s">
+      <c r="G31" s="42" t="s">
         <v>150</v>
       </c>
-      <c r="H31" s="57" t="s">
+      <c r="H31" s="42" t="s">
         <v>149</v>
       </c>
-      <c r="I31" s="57" t="s">
+      <c r="I31" s="42" t="s">
         <v>151</v>
       </c>
-      <c r="J31" s="57" t="s">
+      <c r="J31" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="K31" s="57" t="s">
+      <c r="K31" s="42" t="s">
         <v>153</v>
       </c>
       <c r="L31" s="35"/>
     </row>
-    <row r="32" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B32" s="56" t="s">
         <v>154</v>
       </c>
-      <c r="C32" s="57" t="s">
+      <c r="C32" s="42" t="s">
         <v>155</v>
       </c>
-      <c r="D32" s="57" t="s">
+      <c r="D32" s="42" t="s">
         <v>156</v>
       </c>
-      <c r="E32" s="57" t="s">
+      <c r="E32" s="42" t="s">
         <v>155</v>
       </c>
-      <c r="F32" s="57" t="s">
+      <c r="F32" s="42" t="s">
         <v>157</v>
       </c>
-      <c r="G32" s="57" t="s">
+      <c r="G32" s="42" t="s">
         <v>158</v>
       </c>
-      <c r="H32" s="57" t="s">
+      <c r="H32" s="42" t="s">
         <v>155</v>
       </c>
-      <c r="I32" s="57" t="s">
+      <c r="I32" s="42" t="s">
         <v>157</v>
       </c>
-      <c r="J32" s="57" t="s">
+      <c r="J32" s="42" t="s">
         <v>159</v>
       </c>
-      <c r="K32" s="57" t="s">
+      <c r="K32" s="42" t="s">
         <v>160</v>
       </c>
       <c r="L32" s="35"/>
     </row>
-    <row r="33" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="56" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B33" s="56" t="s">
         <v>161</v>
       </c>
-      <c r="C33" s="57" t="s">
+      <c r="C33" s="42" t="s">
         <v>162</v>
       </c>
-      <c r="D33" s="57" t="s">
+      <c r="D33" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="E33" s="57" t="s">
+      <c r="E33" s="42" t="s">
         <v>162</v>
       </c>
-      <c r="F33" s="57" t="s">
+      <c r="F33" s="42" t="s">
         <v>164</v>
       </c>
-      <c r="G33" s="57" t="s">
+      <c r="G33" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="H33" s="57" t="s">
+      <c r="H33" s="42" t="s">
         <v>162</v>
       </c>
-      <c r="I33" s="57" t="s">
+      <c r="I33" s="42" t="s">
         <v>164</v>
       </c>
-      <c r="J33" s="57" t="s">
+      <c r="J33" s="42" t="s">
         <v>165</v>
       </c>
-      <c r="K33" s="57" t="s">
+      <c r="K33" s="42" t="s">
         <v>166</v>
       </c>
       <c r="L33" s="35"/>
     </row>
-    <row r="34" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="56" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B34" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="C34" s="57" t="s">
+      <c r="C34" s="42" t="s">
         <v>168</v>
       </c>
-      <c r="D34" s="57" t="s">
+      <c r="D34" s="42" t="s">
         <v>169</v>
       </c>
-      <c r="E34" s="57" t="s">
+      <c r="E34" s="42" t="s">
         <v>168</v>
       </c>
-      <c r="F34" s="57" t="s">
+      <c r="F34" s="42" t="s">
         <v>170</v>
       </c>
-      <c r="G34" s="57" t="s">
+      <c r="G34" s="42" t="s">
         <v>171</v>
       </c>
-      <c r="H34" s="57" t="s">
+      <c r="H34" s="42" t="s">
         <v>172</v>
       </c>
-      <c r="I34" s="57" t="s">
+      <c r="I34" s="42" t="s">
         <v>173</v>
       </c>
-      <c r="J34" s="57" t="s">
+      <c r="J34" s="42" t="s">
         <v>174</v>
       </c>
-      <c r="K34" s="57" t="s">
+      <c r="K34" s="42" t="s">
         <v>175</v>
       </c>
       <c r="L34" s="35"/>
     </row>
-    <row r="35" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="56" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B35" s="56" t="s">
         <v>176</v>
       </c>
-      <c r="C35" s="57" t="s">
+      <c r="C35" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="D35" s="57" t="s">
+      <c r="D35" s="42" t="s">
         <v>178</v>
       </c>
-      <c r="E35" s="57" t="s">
+      <c r="E35" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="F35" s="57" t="s">
+      <c r="F35" s="42" t="s">
         <v>179</v>
       </c>
-      <c r="G35" s="57" t="s">
+      <c r="G35" s="42" t="s">
         <v>180</v>
       </c>
-      <c r="H35" s="57" t="s">
+      <c r="H35" s="42" t="s">
         <v>181</v>
       </c>
-      <c r="I35" s="57" t="s">
+      <c r="I35" s="42" t="s">
         <v>182</v>
       </c>
-      <c r="J35" s="57" t="s">
+      <c r="J35" s="42" t="s">
         <v>183</v>
       </c>
-      <c r="K35" s="57" t="s">
+      <c r="K35" s="42" t="s">
         <v>184</v>
       </c>
       <c r="L35" s="35"/>
     </row>
-    <row r="36" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="56" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B36" s="56" t="s">
         <v>185</v>
       </c>
-      <c r="C36" s="57" t="s">
+      <c r="C36" s="42" t="s">
         <v>186</v>
       </c>
-      <c r="D36" s="57" t="s">
+      <c r="D36" s="42" t="s">
         <v>187</v>
       </c>
-      <c r="E36" s="57" t="s">
+      <c r="E36" s="42" t="s">
         <v>186</v>
       </c>
-      <c r="F36" s="57" t="s">
+      <c r="F36" s="42" t="s">
         <v>188</v>
       </c>
-      <c r="G36" s="57" t="s">
+      <c r="G36" s="42" t="s">
         <v>189</v>
       </c>
-      <c r="H36" s="57" t="s">
+      <c r="H36" s="42" t="s">
         <v>190</v>
       </c>
-      <c r="I36" s="57" t="s">
+      <c r="I36" s="42" t="s">
         <v>191</v>
       </c>
-      <c r="J36" s="57" t="s">
+      <c r="J36" s="42" t="s">
         <v>192</v>
       </c>
-      <c r="K36" s="57" t="s">
+      <c r="K36" s="42" t="s">
         <v>193</v>
       </c>
       <c r="L36" s="35"/>
     </row>
-    <row r="37" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="56" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B37" s="56" t="s">
         <v>194</v>
       </c>
-      <c r="C37" s="57" t="s">
+      <c r="C37" s="42" t="s">
         <v>195</v>
       </c>
-      <c r="D37" s="57" t="s">
+      <c r="D37" s="42" t="s">
         <v>196</v>
       </c>
-      <c r="E37" s="57" t="s">
+      <c r="E37" s="42" t="s">
         <v>195</v>
       </c>
-      <c r="F37" s="57" t="s">
+      <c r="F37" s="42" t="s">
         <v>197</v>
       </c>
-      <c r="G37" s="57" t="s">
+      <c r="G37" s="42" t="s">
         <v>198</v>
       </c>
-      <c r="H37" s="57" t="s">
+      <c r="H37" s="42" t="s">
         <v>199</v>
       </c>
-      <c r="I37" s="57" t="s">
+      <c r="I37" s="42" t="s">
         <v>200</v>
       </c>
-      <c r="J37" s="57" t="s">
+      <c r="J37" s="42" t="s">
         <v>201</v>
       </c>
-      <c r="K37" s="57" t="s">
+      <c r="K37" s="42" t="s">
         <v>202</v>
       </c>
       <c r="L37" s="35"/>
     </row>
-    <row r="38" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="56" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B38" s="56" t="s">
         <v>203</v>
       </c>
-      <c r="C38" s="57" t="s">
+      <c r="C38" s="42" t="s">
         <v>204</v>
       </c>
-      <c r="D38" s="57" t="s">
+      <c r="D38" s="42" t="s">
         <v>205</v>
       </c>
-      <c r="E38" s="57" t="s">
+      <c r="E38" s="42" t="s">
         <v>204</v>
       </c>
-      <c r="F38" s="57" t="s">
+      <c r="F38" s="42" t="s">
         <v>206</v>
       </c>
-      <c r="G38" s="57" t="s">
+      <c r="G38" s="42" t="s">
         <v>207</v>
       </c>
-      <c r="H38" s="57" t="s">
+      <c r="H38" s="42" t="s">
         <v>208</v>
       </c>
-      <c r="I38" s="57" t="s">
+      <c r="I38" s="42" t="s">
         <v>209</v>
       </c>
-      <c r="J38" s="57" t="s">
+      <c r="J38" s="42" t="s">
         <v>210</v>
       </c>
-      <c r="K38" s="57" t="s">
+      <c r="K38" s="42" t="s">
         <v>211</v>
       </c>
       <c r="L38" s="35"/>
     </row>
-    <row r="39" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="56" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B39" s="56" t="s">
         <v>212</v>
       </c>
-      <c r="C39" s="57" t="s">
+      <c r="C39" s="42" t="s">
         <v>213</v>
       </c>
-      <c r="D39" s="57" t="s">
+      <c r="D39" s="42" t="s">
         <v>214</v>
       </c>
-      <c r="E39" s="57" t="s">
+      <c r="E39" s="42" t="s">
         <v>213</v>
       </c>
-      <c r="F39" s="57" t="s">
+      <c r="F39" s="42" t="s">
         <v>215</v>
       </c>
-      <c r="G39" s="57" t="s">
+      <c r="G39" s="42" t="s">
         <v>216</v>
       </c>
-      <c r="H39" s="57" t="s">
+      <c r="H39" s="42" t="s">
         <v>217</v>
       </c>
-      <c r="I39" s="57" t="s">
+      <c r="I39" s="42" t="s">
         <v>218</v>
       </c>
-      <c r="J39" s="57" t="s">
+      <c r="J39" s="42" t="s">
         <v>219</v>
       </c>
-      <c r="K39" s="57" t="s">
+      <c r="K39" s="42" t="s">
         <v>220</v>
       </c>
       <c r="L39" s="35"/>
     </row>
     <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="58"/>
-      <c r="B40" s="58"/>
-      <c r="C40" s="58"/>
-      <c r="D40" s="58"/>
-      <c r="E40" s="58"/>
-      <c r="F40" s="58"/>
-      <c r="G40" s="58"/>
-      <c r="H40" s="58"/>
-      <c r="I40" s="58"/>
-      <c r="J40" s="59"/>
+      <c r="A40" s="57"/>
+      <c r="B40" s="57"/>
+      <c r="C40" s="57"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="58"/>
       <c r="K40" s="35"/>
       <c r="L40" s="35"/>
     </row>
     <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="58"/>
-      <c r="B41" s="58"/>
-      <c r="C41" s="58"/>
-      <c r="D41" s="58"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="58"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="59"/>
+      <c r="A41" s="57"/>
+      <c r="B41" s="57"/>
+      <c r="C41" s="57"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="57"/>
+      <c r="F41" s="57"/>
+      <c r="G41" s="57"/>
+      <c r="H41" s="57"/>
+      <c r="I41" s="57"/>
+      <c r="J41" s="58"/>
       <c r="K41" s="35"/>
       <c r="L41" s="35"/>
     </row>
     <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="58"/>
-      <c r="B42" s="58"/>
-      <c r="C42" s="58"/>
-      <c r="D42" s="58"/>
-      <c r="E42" s="58"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="58"/>
-      <c r="H42" s="58"/>
-      <c r="I42" s="58"/>
-      <c r="J42" s="59"/>
+      <c r="A42" s="57"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="57"/>
+      <c r="H42" s="57"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="58"/>
       <c r="K42" s="35"/>
       <c r="L42" s="35"/>
     </row>
     <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="58"/>
-      <c r="B43" s="58"/>
-      <c r="C43" s="58"/>
-      <c r="D43" s="58"/>
-      <c r="E43" s="58"/>
-      <c r="F43" s="58"/>
-      <c r="G43" s="58"/>
-      <c r="H43" s="58"/>
-      <c r="I43" s="58"/>
-      <c r="J43" s="59"/>
+      <c r="A43" s="57"/>
+      <c r="B43" s="57"/>
+      <c r="C43" s="57"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="57"/>
+      <c r="F43" s="57"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="57"/>
+      <c r="I43" s="57"/>
+      <c r="J43" s="58"/>
       <c r="K43" s="35"/>
       <c r="L43" s="35"/>
     </row>
     <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="58"/>
-      <c r="B44" s="58"/>
-      <c r="C44" s="58"/>
-      <c r="D44" s="58"/>
-      <c r="E44" s="58"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="58"/>
-      <c r="H44" s="58"/>
-      <c r="I44" s="58"/>
-      <c r="J44" s="59"/>
+      <c r="A44" s="57"/>
+      <c r="B44" s="57"/>
+      <c r="C44" s="57"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="57"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="57"/>
+      <c r="J44" s="58"/>
       <c r="K44" s="35"/>
       <c r="L44" s="35"/>
     </row>
     <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="58"/>
-      <c r="B45" s="58"/>
-      <c r="C45" s="58"/>
-      <c r="D45" s="58"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="58"/>
-      <c r="H45" s="58"/>
-      <c r="I45" s="58"/>
-      <c r="J45" s="59"/>
+      <c r="A45" s="57"/>
+      <c r="B45" s="57"/>
+      <c r="C45" s="57"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="57"/>
+      <c r="J45" s="58"/>
       <c r="K45" s="35"/>
     </row>
     <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="58"/>
-      <c r="B46" s="58"/>
-      <c r="C46" s="58"/>
-      <c r="D46" s="58"/>
-      <c r="E46" s="58"/>
-      <c r="F46" s="58"/>
-      <c r="G46" s="58"/>
-      <c r="H46" s="58"/>
-      <c r="I46" s="58"/>
-      <c r="J46" s="59"/>
+      <c r="A46" s="57"/>
+      <c r="B46" s="57"/>
+      <c r="C46" s="57"/>
+      <c r="D46" s="57"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="57"/>
+      <c r="G46" s="57"/>
+      <c r="H46" s="57"/>
+      <c r="I46" s="57"/>
+      <c r="J46" s="58"/>
       <c r="K46" s="35"/>
     </row>
     <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="58"/>
-      <c r="B47" s="58"/>
-      <c r="C47" s="58"/>
-      <c r="D47" s="58"/>
-      <c r="E47" s="58"/>
-      <c r="F47" s="58"/>
-      <c r="G47" s="58"/>
-      <c r="H47" s="58"/>
-      <c r="I47" s="58"/>
-      <c r="J47" s="59"/>
+      <c r="A47" s="57"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="57"/>
+      <c r="G47" s="57"/>
+      <c r="H47" s="57"/>
+      <c r="I47" s="57"/>
+      <c r="J47" s="58"/>
       <c r="K47" s="35"/>
     </row>
     <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="58"/>
-      <c r="B48" s="58"/>
-      <c r="C48" s="58"/>
-      <c r="D48" s="58"/>
-      <c r="E48" s="58"/>
-      <c r="F48" s="58"/>
-      <c r="G48" s="58"/>
-      <c r="H48" s="58"/>
-      <c r="I48" s="58"/>
-      <c r="J48" s="59"/>
+      <c r="A48" s="57"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="57"/>
+      <c r="D48" s="57"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="57"/>
+      <c r="G48" s="57"/>
+      <c r="H48" s="57"/>
+      <c r="I48" s="57"/>
+      <c r="J48" s="58"/>
       <c r="K48" s="35"/>
     </row>
     <row r="49" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6748,7 +6744,7 @@
       <c r="J56" s="35"/>
       <c r="K56" s="35"/>
     </row>
-    <row r="57" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="54" t="s">
         <v>91</v>
       </c>
@@ -6790,31 +6786,31 @@
       <c r="B58" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="C58" s="57" t="s">
+      <c r="C58" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="D58" s="57" t="s">
+      <c r="D58" s="42" t="s">
         <v>222</v>
       </c>
-      <c r="E58" s="57" t="s">
+      <c r="E58" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="F58" s="57" t="s">
+      <c r="F58" s="42" t="s">
         <v>223</v>
       </c>
-      <c r="G58" s="57" t="s">
+      <c r="G58" s="42" t="s">
         <v>224</v>
       </c>
-      <c r="H58" s="57" t="s">
+      <c r="H58" s="42" t="s">
         <v>225</v>
       </c>
-      <c r="I58" s="57" t="s">
+      <c r="I58" s="42" t="s">
         <v>226</v>
       </c>
-      <c r="J58" s="57" t="s">
+      <c r="J58" s="42" t="s">
         <v>227</v>
       </c>
-      <c r="K58" s="57" t="s">
+      <c r="K58" s="42" t="s">
         <v>228</v>
       </c>
     </row>
@@ -6825,486 +6821,486 @@
       <c r="B59" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="C59" s="57" t="s">
+      <c r="C59" s="42" t="s">
         <v>229</v>
       </c>
-      <c r="D59" s="57" t="s">
+      <c r="D59" s="42" t="s">
         <v>230</v>
       </c>
-      <c r="E59" s="57" t="s">
+      <c r="E59" s="42" t="s">
         <v>229</v>
       </c>
-      <c r="F59" s="57" t="s">
+      <c r="F59" s="42" t="s">
         <v>231</v>
       </c>
-      <c r="G59" s="57" t="s">
+      <c r="G59" s="42" t="s">
         <v>232</v>
       </c>
-      <c r="H59" s="57" t="s">
+      <c r="H59" s="42" t="s">
         <v>233</v>
       </c>
-      <c r="I59" s="57" t="s">
+      <c r="I59" s="42" t="s">
         <v>234</v>
       </c>
-      <c r="J59" s="57" t="s">
+      <c r="J59" s="42" t="s">
         <v>235</v>
       </c>
-      <c r="K59" s="57" t="s">
+      <c r="K59" s="42" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B60" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="C60" s="57" t="s">
+      <c r="C60" s="42" t="s">
         <v>237</v>
       </c>
-      <c r="D60" s="57" t="s">
+      <c r="D60" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="E60" s="57" t="s">
+      <c r="E60" s="42" t="s">
         <v>237</v>
       </c>
-      <c r="F60" s="57" t="s">
+      <c r="F60" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="G60" s="57" t="s">
+      <c r="G60" s="42" t="s">
         <v>240</v>
       </c>
-      <c r="H60" s="57" t="s">
+      <c r="H60" s="42" t="s">
         <v>241</v>
       </c>
-      <c r="I60" s="57" t="s">
+      <c r="I60" s="42" t="s">
         <v>242</v>
       </c>
-      <c r="J60" s="57" t="s">
+      <c r="J60" s="42" t="s">
         <v>243</v>
       </c>
-      <c r="K60" s="57" t="s">
+      <c r="K60" s="42" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B61" s="56" t="s">
         <v>129</v>
       </c>
-      <c r="C61" s="57" t="s">
+      <c r="C61" s="42" t="s">
         <v>245</v>
       </c>
-      <c r="D61" s="57" t="s">
+      <c r="D61" s="42" t="s">
         <v>246</v>
       </c>
-      <c r="E61" s="57" t="s">
+      <c r="E61" s="42" t="s">
         <v>245</v>
       </c>
-      <c r="F61" s="57" t="s">
+      <c r="F61" s="42" t="s">
         <v>247</v>
       </c>
-      <c r="G61" s="57" t="s">
+      <c r="G61" s="42" t="s">
         <v>248</v>
       </c>
-      <c r="H61" s="57" t="s">
+      <c r="H61" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="I61" s="57" t="s">
+      <c r="I61" s="42" t="s">
         <v>250</v>
       </c>
-      <c r="J61" s="57" t="s">
+      <c r="J61" s="42" t="s">
         <v>251</v>
       </c>
-      <c r="K61" s="57" t="s">
+      <c r="K61" s="42" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B62" s="56" t="s">
         <v>136</v>
       </c>
-      <c r="C62" s="57" t="s">
+      <c r="C62" s="42" t="s">
         <v>253</v>
       </c>
-      <c r="D62" s="57" t="s">
+      <c r="D62" s="42" t="s">
         <v>254</v>
       </c>
-      <c r="E62" s="57" t="s">
+      <c r="E62" s="42" t="s">
         <v>253</v>
       </c>
-      <c r="F62" s="57" t="s">
+      <c r="F62" s="42" t="s">
         <v>255</v>
       </c>
-      <c r="G62" s="57" t="s">
+      <c r="G62" s="42" t="s">
         <v>256</v>
       </c>
-      <c r="H62" s="57" t="s">
+      <c r="H62" s="42" t="s">
         <v>257</v>
       </c>
-      <c r="I62" s="57" t="s">
+      <c r="I62" s="42" t="s">
         <v>258</v>
       </c>
-      <c r="J62" s="57" t="s">
+      <c r="J62" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="K62" s="57" t="s">
+      <c r="K62" s="42" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="56" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B63" s="56" t="s">
         <v>142</v>
       </c>
-      <c r="C63" s="57" t="s">
+      <c r="C63" s="42" t="s">
         <v>261</v>
       </c>
-      <c r="D63" s="57" t="s">
+      <c r="D63" s="42" t="s">
         <v>262</v>
       </c>
-      <c r="E63" s="57" t="s">
+      <c r="E63" s="42" t="s">
         <v>261</v>
       </c>
-      <c r="F63" s="57" t="s">
+      <c r="F63" s="42" t="s">
         <v>263</v>
       </c>
-      <c r="G63" s="57" t="s">
+      <c r="G63" s="42" t="s">
         <v>264</v>
       </c>
-      <c r="H63" s="57" t="s">
+      <c r="H63" s="42" t="s">
         <v>265</v>
       </c>
-      <c r="I63" s="57" t="s">
+      <c r="I63" s="42" t="s">
         <v>266</v>
       </c>
-      <c r="J63" s="57" t="s">
+      <c r="J63" s="42" t="s">
         <v>267</v>
       </c>
-      <c r="K63" s="57" t="s">
+      <c r="K63" s="42" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="56" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B64" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="C64" s="57" t="s">
+      <c r="C64" s="42" t="s">
         <v>269</v>
       </c>
-      <c r="D64" s="57" t="s">
+      <c r="D64" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="E64" s="57" t="s">
+      <c r="E64" s="42" t="s">
         <v>269</v>
       </c>
-      <c r="F64" s="57" t="s">
+      <c r="F64" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="G64" s="57" t="s">
+      <c r="G64" s="42" t="s">
         <v>272</v>
       </c>
-      <c r="H64" s="57" t="s">
+      <c r="H64" s="42" t="s">
         <v>273</v>
       </c>
-      <c r="I64" s="57" t="s">
+      <c r="I64" s="42" t="s">
         <v>274</v>
       </c>
-      <c r="J64" s="57" t="s">
+      <c r="J64" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="K64" s="57" t="s">
+      <c r="K64" s="42" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B65" s="56" t="s">
         <v>154</v>
       </c>
-      <c r="C65" s="57" t="s">
+      <c r="C65" s="42" t="s">
         <v>277</v>
       </c>
-      <c r="D65" s="57" t="s">
+      <c r="D65" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="E65" s="57" t="s">
+      <c r="E65" s="42" t="s">
         <v>277</v>
       </c>
-      <c r="F65" s="57" t="s">
+      <c r="F65" s="42" t="s">
         <v>279</v>
       </c>
-      <c r="G65" s="57" t="s">
+      <c r="G65" s="42" t="s">
         <v>280</v>
       </c>
-      <c r="H65" s="57" t="s">
+      <c r="H65" s="42" t="s">
         <v>281</v>
       </c>
-      <c r="I65" s="57" t="s">
+      <c r="I65" s="42" t="s">
         <v>282</v>
       </c>
-      <c r="J65" s="57" t="s">
+      <c r="J65" s="42" t="s">
         <v>283</v>
       </c>
-      <c r="K65" s="57" t="s">
+      <c r="K65" s="42" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="56" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B66" s="56" t="s">
         <v>161</v>
       </c>
-      <c r="C66" s="57" t="s">
+      <c r="C66" s="42" t="s">
         <v>285</v>
       </c>
-      <c r="D66" s="57" t="s">
+      <c r="D66" s="42" t="s">
         <v>286</v>
       </c>
-      <c r="E66" s="57" t="s">
+      <c r="E66" s="42" t="s">
         <v>285</v>
       </c>
-      <c r="F66" s="57" t="s">
+      <c r="F66" s="42" t="s">
         <v>287</v>
       </c>
-      <c r="G66" s="57" t="s">
+      <c r="G66" s="42" t="s">
         <v>288</v>
       </c>
-      <c r="H66" s="57" t="s">
+      <c r="H66" s="42" t="s">
         <v>289</v>
       </c>
-      <c r="I66" s="57" t="s">
+      <c r="I66" s="42" t="s">
         <v>290</v>
       </c>
-      <c r="J66" s="57" t="s">
+      <c r="J66" s="42" t="s">
         <v>291</v>
       </c>
-      <c r="K66" s="57" t="s">
+      <c r="K66" s="42" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="56" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B67" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="C67" s="57" t="s">
+      <c r="C67" s="42" t="s">
         <v>293</v>
       </c>
-      <c r="D67" s="57" t="s">
+      <c r="D67" s="42" t="s">
         <v>294</v>
       </c>
-      <c r="E67" s="57" t="s">
+      <c r="E67" s="42" t="s">
         <v>293</v>
       </c>
-      <c r="F67" s="57" t="s">
+      <c r="F67" s="42" t="s">
         <v>295</v>
       </c>
-      <c r="G67" s="57" t="s">
+      <c r="G67" s="42" t="s">
         <v>296</v>
       </c>
-      <c r="H67" s="57" t="s">
+      <c r="H67" s="42" t="s">
         <v>297</v>
       </c>
-      <c r="I67" s="57" t="s">
+      <c r="I67" s="42" t="s">
         <v>298</v>
       </c>
-      <c r="J67" s="57" t="s">
+      <c r="J67" s="42" t="s">
         <v>299</v>
       </c>
-      <c r="K67" s="57" t="s">
+      <c r="K67" s="42" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="56" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B68" s="56" t="s">
         <v>176</v>
       </c>
-      <c r="C68" s="57" t="s">
+      <c r="C68" s="42" t="s">
         <v>301</v>
       </c>
-      <c r="D68" s="57" t="s">
+      <c r="D68" s="42" t="s">
         <v>302</v>
       </c>
-      <c r="E68" s="57" t="s">
+      <c r="E68" s="42" t="s">
         <v>301</v>
       </c>
-      <c r="F68" s="57" t="s">
+      <c r="F68" s="42" t="s">
         <v>303</v>
       </c>
-      <c r="G68" s="57" t="s">
+      <c r="G68" s="42" t="s">
         <v>304</v>
       </c>
-      <c r="H68" s="57" t="s">
+      <c r="H68" s="42" t="s">
         <v>305</v>
       </c>
-      <c r="I68" s="57" t="s">
+      <c r="I68" s="42" t="s">
         <v>306</v>
       </c>
-      <c r="J68" s="57" t="s">
+      <c r="J68" s="42" t="s">
         <v>307</v>
       </c>
-      <c r="K68" s="57" t="s">
+      <c r="K68" s="42" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="56" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B69" s="56" t="s">
         <v>185</v>
       </c>
-      <c r="C69" s="57" t="s">
+      <c r="C69" s="42" t="s">
         <v>309</v>
       </c>
-      <c r="D69" s="57" t="s">
+      <c r="D69" s="42" t="s">
         <v>310</v>
       </c>
-      <c r="E69" s="57" t="s">
+      <c r="E69" s="42" t="s">
         <v>309</v>
       </c>
-      <c r="F69" s="57" t="s">
+      <c r="F69" s="42" t="s">
         <v>311</v>
       </c>
-      <c r="G69" s="57" t="s">
+      <c r="G69" s="42" t="s">
         <v>312</v>
       </c>
-      <c r="H69" s="57" t="s">
+      <c r="H69" s="42" t="s">
         <v>313</v>
       </c>
-      <c r="I69" s="57" t="s">
+      <c r="I69" s="42" t="s">
         <v>314</v>
       </c>
-      <c r="J69" s="57" t="s">
+      <c r="J69" s="42" t="s">
         <v>315</v>
       </c>
-      <c r="K69" s="57" t="s">
+      <c r="K69" s="42" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="56" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B70" s="56" t="s">
         <v>194</v>
       </c>
-      <c r="C70" s="57" t="s">
+      <c r="C70" s="42" t="s">
         <v>317</v>
       </c>
-      <c r="D70" s="57" t="s">
+      <c r="D70" s="42" t="s">
         <v>318</v>
       </c>
-      <c r="E70" s="57" t="s">
+      <c r="E70" s="42" t="s">
         <v>317</v>
       </c>
-      <c r="F70" s="57" t="s">
+      <c r="F70" s="42" t="s">
         <v>319</v>
       </c>
-      <c r="G70" s="57" t="s">
+      <c r="G70" s="42" t="s">
         <v>320</v>
       </c>
-      <c r="H70" s="57" t="s">
+      <c r="H70" s="42" t="s">
         <v>321</v>
       </c>
-      <c r="I70" s="57" t="s">
+      <c r="I70" s="42" t="s">
         <v>322</v>
       </c>
-      <c r="J70" s="57" t="s">
+      <c r="J70" s="42" t="s">
         <v>323</v>
       </c>
-      <c r="K70" s="57" t="s">
+      <c r="K70" s="42" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="56" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B71" s="56" t="s">
         <v>203</v>
       </c>
-      <c r="C71" s="57" t="s">
+      <c r="C71" s="42" t="s">
         <v>325</v>
       </c>
-      <c r="D71" s="57" t="s">
+      <c r="D71" s="42" t="s">
         <v>326</v>
       </c>
-      <c r="E71" s="57" t="s">
+      <c r="E71" s="42" t="s">
         <v>325</v>
       </c>
-      <c r="F71" s="57" t="s">
+      <c r="F71" s="42" t="s">
         <v>327</v>
       </c>
-      <c r="G71" s="57" t="s">
+      <c r="G71" s="42" t="s">
         <v>328</v>
       </c>
-      <c r="H71" s="57" t="s">
+      <c r="H71" s="42" t="s">
         <v>329</v>
       </c>
-      <c r="I71" s="57" t="s">
+      <c r="I71" s="42" t="s">
         <v>330</v>
       </c>
-      <c r="J71" s="57" t="s">
+      <c r="J71" s="42" t="s">
         <v>331</v>
       </c>
-      <c r="K71" s="57" t="s">
+      <c r="K71" s="42" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="56" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B72" s="56" t="s">
         <v>212</v>
       </c>
-      <c r="C72" s="57" t="s">
+      <c r="C72" s="42" t="s">
         <v>333</v>
       </c>
-      <c r="D72" s="57" t="s">
+      <c r="D72" s="42" t="s">
         <v>334</v>
       </c>
-      <c r="E72" s="57" t="s">
+      <c r="E72" s="42" t="s">
         <v>333</v>
       </c>
-      <c r="F72" s="57" t="s">
+      <c r="F72" s="42" t="s">
         <v>335</v>
       </c>
-      <c r="G72" s="57" t="s">
+      <c r="G72" s="42" t="s">
         <v>336</v>
       </c>
-      <c r="H72" s="57" t="s">
+      <c r="H72" s="42" t="s">
         <v>337</v>
       </c>
-      <c r="I72" s="57" t="s">
+      <c r="I72" s="42" t="s">
         <v>338</v>
       </c>
-      <c r="J72" s="57" t="s">
+      <c r="J72" s="42" t="s">
         <v>339</v>
       </c>
-      <c r="K72" s="57" t="s">
+      <c r="K72" s="42" t="s">
         <v>340</v>
       </c>
     </row>
@@ -7336,7 +7332,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="35" width="71.46"/>
   </cols>
   <sheetData>
-    <row r="1" s="61" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="60" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -7355,8 +7351,8 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
     </row>
     <row r="2" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
@@ -7375,8 +7371,8 @@
         <v>343</v>
       </c>
       <c r="F2" s="7"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
     </row>
     <row r="3" customFormat="false" ht="135.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
@@ -7395,8 +7391,8 @@
         <v>345</v>
       </c>
       <c r="F3" s="11"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
     </row>
     <row r="4" customFormat="false" ht="20.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12"/>
@@ -7405,8 +7401,8 @@
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
       <c r="F4" s="12"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
     </row>
     <row r="5" customFormat="false" ht="76.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
@@ -7423,8 +7419,8 @@
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="16"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
     </row>
     <row r="6" customFormat="false" ht="23.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17"/>
@@ -7433,8 +7429,8 @@
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
       <c r="F6" s="20"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
     </row>
     <row r="7" customFormat="false" ht="101.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
@@ -7451,8 +7447,8 @@
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="16"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="62"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
     </row>
     <row r="8" customFormat="false" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="17"/>
@@ -7461,8 +7457,8 @@
       <c r="D8" s="19"/>
       <c r="E8" s="19"/>
       <c r="F8" s="20"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
     </row>
     <row r="9" customFormat="false" ht="101.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
@@ -7479,8 +7475,8 @@
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="16"/>
-      <c r="G9" s="62"/>
-      <c r="H9" s="62"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
     </row>
     <row r="10" customFormat="false" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="17"/>
@@ -7489,8 +7485,8 @@
       <c r="D10" s="19"/>
       <c r="E10" s="19"/>
       <c r="F10" s="20"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
     </row>
     <row r="11" s="1" customFormat="true" ht="97.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
@@ -7509,8 +7505,8 @@
         <v>351</v>
       </c>
       <c r="F11" s="24"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="62"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
     </row>
     <row r="12" s="1" customFormat="true" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="25"/>
@@ -7519,8 +7515,8 @@
       <c r="D12" s="27"/>
       <c r="E12" s="27"/>
       <c r="F12" s="28"/>
-      <c r="G12" s="62"/>
-      <c r="H12" s="62"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
     </row>
     <row r="13" s="1" customFormat="true" ht="118" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="29" t="s">
@@ -7537,8 +7533,8 @@
       </c>
       <c r="E13" s="30"/>
       <c r="F13" s="32"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
     </row>
     <row r="14" s="1" customFormat="true" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33"/>
@@ -7547,8 +7543,8 @@
       <c r="D14" s="34"/>
       <c r="E14" s="34"/>
       <c r="F14" s="35"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
     </row>
     <row r="15" s="1" customFormat="true" ht="111.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="29" t="s">
@@ -7565,8 +7561,8 @@
       </c>
       <c r="E15" s="30"/>
       <c r="F15" s="32"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="62"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="61"/>
     </row>
     <row r="16" s="12" customFormat="true" ht="20.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="33"/>
@@ -7575,8 +7571,8 @@
       <c r="D16" s="34"/>
       <c r="E16" s="34"/>
       <c r="F16" s="35"/>
-      <c r="G16" s="62"/>
-      <c r="H16" s="62"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="61"/>
     </row>
     <row r="17" customFormat="false" ht="104.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="29" t="s">
@@ -7593,12 +7589,12 @@
       </c>
       <c r="E17" s="30"/>
       <c r="F17" s="32"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="61"/>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
     </row>
     <row r="19" customFormat="false" ht="97.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="29" t="s">
@@ -7617,12 +7613,12 @@
         <v>357</v>
       </c>
       <c r="F19" s="32"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="61"/>
     </row>
     <row r="20" customFormat="false" ht="17.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
     </row>
     <row r="21" customFormat="false" ht="159.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="29" t="s">
@@ -7681,8 +7677,8 @@
       <c r="F25" s="32"/>
     </row>
     <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="61"/>
     </row>
     <row r="27" customFormat="false" ht="97.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="29" t="s">
@@ -7701,12 +7697,12 @@
         <v>363</v>
       </c>
       <c r="F27" s="32"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="61"/>
     </row>
     <row r="28" customFormat="false" ht="17.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
+      <c r="G28" s="61"/>
+      <c r="H28" s="61"/>
     </row>
     <row r="29" customFormat="false" ht="159.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="29" t="s">
@@ -7765,8 +7761,8 @@
       <c r="F33" s="32"/>
     </row>
     <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G34" s="62"/>
-      <c r="H34" s="62"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="61"/>
     </row>
     <row r="35" customFormat="false" ht="100.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="29" t="s">
@@ -7785,12 +7781,12 @@
         <v>369</v>
       </c>
       <c r="F35" s="32"/>
-      <c r="G35" s="62"/>
-      <c r="H35" s="62"/>
+      <c r="G35" s="61"/>
+      <c r="H35" s="61"/>
     </row>
     <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G36" s="62"/>
-      <c r="H36" s="62"/>
+      <c r="G36" s="61"/>
+      <c r="H36" s="61"/>
     </row>
     <row r="37" customFormat="false" ht="108.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="29" t="s">
@@ -7807,13 +7803,13 @@
       </c>
       <c r="E37" s="30"/>
       <c r="F37" s="32"/>
-      <c r="G37" s="62"/>
-      <c r="H37" s="62"/>
+      <c r="G37" s="61"/>
+      <c r="H37" s="61"/>
     </row>
     <row r="38" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="33"/>
-      <c r="G38" s="62"/>
-      <c r="H38" s="62"/>
+      <c r="G38" s="61"/>
+      <c r="H38" s="61"/>
     </row>
     <row r="39" customFormat="false" ht="88.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="29" t="s">
@@ -7830,13 +7826,13 @@
       </c>
       <c r="E39" s="30"/>
       <c r="F39" s="32"/>
-      <c r="G39" s="62"/>
-      <c r="H39" s="62"/>
+      <c r="G39" s="61"/>
+      <c r="H39" s="61"/>
     </row>
     <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="33"/>
-      <c r="G40" s="62"/>
-      <c r="H40" s="62"/>
+      <c r="G40" s="61"/>
+      <c r="H40" s="61"/>
     </row>
     <row r="41" customFormat="false" ht="98.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="29" t="s">
@@ -7853,64 +7849,64 @@
       </c>
       <c r="E41" s="30"/>
       <c r="F41" s="32"/>
-      <c r="G41" s="62"/>
-      <c r="H41" s="62"/>
+      <c r="G41" s="61"/>
+      <c r="H41" s="61"/>
     </row>
     <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G42" s="62"/>
-      <c r="H42" s="62"/>
+      <c r="G42" s="61"/>
+      <c r="H42" s="61"/>
     </row>
     <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G43" s="62"/>
-      <c r="H43" s="62"/>
+      <c r="G43" s="61"/>
+      <c r="H43" s="61"/>
     </row>
     <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G44" s="62"/>
-      <c r="H44" s="62"/>
+      <c r="G44" s="61"/>
+      <c r="H44" s="61"/>
     </row>
     <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G45" s="62"/>
-      <c r="H45" s="62"/>
+      <c r="G45" s="61"/>
+      <c r="H45" s="61"/>
     </row>
     <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G46" s="62"/>
-      <c r="H46" s="62"/>
+      <c r="G46" s="61"/>
+      <c r="H46" s="61"/>
     </row>
     <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G47" s="62"/>
-      <c r="H47" s="62"/>
+      <c r="G47" s="61"/>
+      <c r="H47" s="61"/>
     </row>
     <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G48" s="62"/>
-      <c r="H48" s="62"/>
+      <c r="G48" s="61"/>
+      <c r="H48" s="61"/>
     </row>
     <row r="49" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G49" s="62"/>
-      <c r="H49" s="62"/>
+      <c r="G49" s="61"/>
+      <c r="H49" s="61"/>
     </row>
     <row r="50" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G50" s="62"/>
-      <c r="H50" s="62"/>
+      <c r="G50" s="61"/>
+      <c r="H50" s="61"/>
     </row>
     <row r="51" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G51" s="62"/>
-      <c r="H51" s="62"/>
+      <c r="G51" s="61"/>
+      <c r="H51" s="61"/>
     </row>
     <row r="52" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G52" s="62"/>
-      <c r="H52" s="62"/>
+      <c r="G52" s="61"/>
+      <c r="H52" s="61"/>
     </row>
     <row r="53" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G53" s="62"/>
-      <c r="H53" s="62"/>
+      <c r="G53" s="61"/>
+      <c r="H53" s="61"/>
     </row>
     <row r="54" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G54" s="62"/>
-      <c r="H54" s="62"/>
+      <c r="G54" s="61"/>
+      <c r="H54" s="61"/>
     </row>
     <row r="55" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G55" s="62"/>
-      <c r="H55" s="62"/>
+      <c r="G55" s="61"/>
+      <c r="H55" s="61"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -7944,35 +7940,35 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="35" width="19.8"/>
   </cols>
   <sheetData>
-    <row r="1" s="70" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="64" t="s">
+    <row r="1" s="69" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="C1" s="64" t="s">
         <v>374</v>
       </c>
-      <c r="D1" s="65" t="s">
+      <c r="D1" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="66" t="s">
+      <c r="E1" s="65" t="s">
         <v>375</v>
       </c>
-      <c r="F1" s="67" t="s">
+      <c r="F1" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="67" t="s">
+      <c r="G1" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="67" t="s">
+      <c r="H1" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="68" t="s">
+      <c r="I1" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="J1" s="69"/>
+      <c r="J1" s="68"/>
       <c r="L1" s="39"/>
       <c r="M1" s="39"/>
       <c r="N1" s="39"/>
@@ -8007,16 +8003,16 @@
       <c r="XFD1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="72" t="n">
+      <c r="B2" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="72" t="n">
+      <c r="C2" s="71" t="n">
         <v>2273097</v>
       </c>
-      <c r="D2" s="73" t="n">
+      <c r="D2" s="72" t="n">
         <v>2095051</v>
       </c>
       <c r="E2" s="42" t="n">
@@ -8067,16 +8063,16 @@
       <c r="AO2" s="35"/>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="70" t="s">
         <v>376</v>
       </c>
-      <c r="B3" s="72" t="n">
+      <c r="B3" s="71" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="72" t="n">
+      <c r="C3" s="71" t="n">
         <v>231073</v>
       </c>
-      <c r="D3" s="73" t="n">
+      <c r="D3" s="72" t="n">
         <v>172846</v>
       </c>
       <c r="E3" s="42" t="n">
@@ -8127,16 +8123,16 @@
       <c r="AO3" s="35"/>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="71" t="s">
+      <c r="A4" s="70" t="s">
         <v>377</v>
       </c>
-      <c r="B4" s="72" t="n">
+      <c r="B4" s="71" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="72" t="n">
+      <c r="C4" s="71" t="n">
         <v>128027</v>
       </c>
-      <c r="D4" s="73" t="n">
+      <c r="D4" s="72" t="n">
         <v>128014</v>
       </c>
       <c r="E4" s="42" t="n">
@@ -8187,16 +8183,16 @@
       <c r="AO4" s="35"/>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="70" t="s">
         <v>378</v>
       </c>
-      <c r="B5" s="72" t="n">
+      <c r="B5" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="72" t="n">
+      <c r="C5" s="71" t="n">
         <v>158930</v>
       </c>
-      <c r="D5" s="73" t="n">
+      <c r="D5" s="72" t="n">
         <v>90694</v>
       </c>
       <c r="E5" s="42" t="n">
@@ -8247,16 +8243,16 @@
       <c r="AO5" s="35"/>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="71" t="s">
+      <c r="A6" s="70" t="s">
         <v>379</v>
       </c>
-      <c r="B6" s="72" t="n">
+      <c r="B6" s="71" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="72" t="n">
+      <c r="C6" s="71" t="n">
         <v>10293</v>
       </c>
-      <c r="D6" s="73" t="n">
+      <c r="D6" s="72" t="n">
         <v>10286</v>
       </c>
       <c r="E6" s="42" t="n">
@@ -8307,16 +8303,16 @@
       <c r="AO6" s="35"/>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="70" t="s">
         <v>380</v>
       </c>
-      <c r="B7" s="72" t="n">
+      <c r="B7" s="71" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="72" t="n">
+      <c r="C7" s="71" t="n">
         <v>7938</v>
       </c>
-      <c r="D7" s="73" t="n">
+      <c r="D7" s="72" t="n">
         <v>5931</v>
       </c>
       <c r="E7" s="42" t="n">
@@ -8367,16 +8363,16 @@
       <c r="AO7" s="35"/>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="70" t="s">
         <v>381</v>
       </c>
-      <c r="B8" s="72" t="n">
+      <c r="B8" s="71" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="72" t="n">
+      <c r="C8" s="71" t="n">
         <v>5796</v>
       </c>
-      <c r="D8" s="73" t="n">
+      <c r="D8" s="72" t="n">
         <v>5385</v>
       </c>
       <c r="E8" s="42" t="n">
@@ -8427,16 +8423,16 @@
       <c r="AO8" s="35"/>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="70" t="s">
         <v>382</v>
       </c>
-      <c r="B9" s="72" t="n">
+      <c r="B9" s="71" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="72" t="n">
+      <c r="C9" s="71" t="n">
         <v>5499</v>
       </c>
-      <c r="D9" s="73" t="n">
+      <c r="D9" s="72" t="n">
         <v>5228</v>
       </c>
       <c r="E9" s="42" t="n">
@@ -8487,16 +8483,16 @@
       <c r="AO9" s="35"/>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="71" t="s">
+      <c r="A10" s="70" t="s">
         <v>383</v>
       </c>
-      <c r="B10" s="72" t="n">
+      <c r="B10" s="71" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="72" t="n">
+      <c r="C10" s="71" t="n">
         <v>5897</v>
       </c>
-      <c r="D10" s="73" t="n">
+      <c r="D10" s="72" t="n">
         <v>3219</v>
       </c>
       <c r="E10" s="42" t="n">
@@ -8547,16 +8543,16 @@
       <c r="AO10" s="35"/>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="71" t="s">
+      <c r="A11" s="70" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="72" t="n">
+      <c r="B11" s="71" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="72" t="n">
+      <c r="C11" s="71" t="n">
         <v>1966</v>
       </c>
-      <c r="D11" s="73" t="n">
+      <c r="D11" s="72" t="n">
         <v>1948</v>
       </c>
       <c r="E11" s="42" t="n">
@@ -8607,16 +8603,16 @@
       <c r="AO11" s="35"/>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="71" t="s">
+      <c r="A12" s="70" t="s">
         <v>384</v>
       </c>
-      <c r="B12" s="72" t="n">
+      <c r="B12" s="71" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="72" t="n">
+      <c r="C12" s="71" t="n">
         <v>1507</v>
       </c>
-      <c r="D12" s="73" t="n">
+      <c r="D12" s="72" t="n">
         <v>1470</v>
       </c>
       <c r="E12" s="42" t="n">
@@ -8667,16 +8663,16 @@
       <c r="AO12" s="35"/>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="71" t="s">
+      <c r="A13" s="70" t="s">
         <v>385</v>
       </c>
-      <c r="B13" s="72" t="n">
+      <c r="B13" s="71" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="72" t="n">
+      <c r="C13" s="71" t="n">
         <v>652</v>
       </c>
-      <c r="D13" s="73" t="n">
+      <c r="D13" s="72" t="n">
         <v>652</v>
       </c>
       <c r="E13" s="42" t="n">
@@ -8697,16 +8693,16 @@
       <c r="K13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="71" t="s">
+      <c r="A14" s="70" t="s">
         <v>386</v>
       </c>
-      <c r="B14" s="72" t="n">
+      <c r="B14" s="71" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="72" t="n">
+      <c r="C14" s="71" t="n">
         <v>36</v>
       </c>
-      <c r="D14" s="73" t="n">
+      <c r="D14" s="72" t="n">
         <v>36</v>
       </c>
       <c r="E14" s="42" t="n">
@@ -8727,16 +8723,16 @@
       <c r="K14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="71" t="s">
+      <c r="A15" s="70" t="s">
         <v>387</v>
       </c>
-      <c r="B15" s="72" t="n">
+      <c r="B15" s="71" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="72" t="n">
+      <c r="C15" s="71" t="n">
         <v>21</v>
       </c>
-      <c r="D15" s="73" t="n">
+      <c r="D15" s="72" t="n">
         <v>21</v>
       </c>
       <c r="E15" s="42" t="n">
@@ -8757,16 +8753,16 @@
       <c r="K15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="74" t="s">
+      <c r="A16" s="73" t="s">
         <v>388</v>
       </c>
-      <c r="B16" s="75" t="n">
+      <c r="B16" s="74" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="75" t="n">
+      <c r="C16" s="74" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="75" t="n">
+      <c r="D16" s="74" t="n">
         <v>11</v>
       </c>
       <c r="E16" s="49" t="n">
@@ -8818,17 +8814,17 @@
       <c r="K17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="76"/>
+      <c r="E18" s="75"/>
       <c r="I18" s="35"/>
       <c r="K18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="76"/>
+      <c r="E19" s="75"/>
       <c r="I19" s="35"/>
       <c r="K19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="77" t="s">
+      <c r="A20" s="76" t="s">
         <v>90</v>
       </c>
       <c r="C20" s="42" t="n">
@@ -8946,7 +8942,7 @@
       <c r="XFC26" s="1"/>
       <c r="XFD26" s="1"/>
     </row>
-    <row r="27" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" s="35" customFormat="true" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="56" t="n">
         <v>1</v>
       </c>
@@ -9011,7 +9007,7 @@
       <c r="AN27" s="1"/>
       <c r="AO27" s="1"/>
     </row>
-    <row r="28" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" s="35" customFormat="true" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="56" t="n">
         <v>2</v>
       </c>
@@ -9076,9 +9072,9 @@
       <c r="AN28" s="1"/>
       <c r="AO28" s="1"/>
     </row>
-    <row r="29" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" s="35" customFormat="true" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B29" s="56" t="s">
         <v>120</v>
@@ -9141,9 +9137,9 @@
       <c r="AN29" s="1"/>
       <c r="AO29" s="1"/>
     </row>
-    <row r="30" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" s="35" customFormat="true" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B30" s="56" t="s">
         <v>129</v>
@@ -9206,9 +9202,9 @@
       <c r="AN30" s="1"/>
       <c r="AO30" s="1"/>
     </row>
-    <row r="31" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" s="35" customFormat="true" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B31" s="56" t="s">
         <v>136</v>
@@ -9271,9 +9267,9 @@
       <c r="AN31" s="1"/>
       <c r="AO31" s="1"/>
     </row>
-    <row r="32" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" s="35" customFormat="true" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="56" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B32" s="56" t="s">
         <v>142</v>
@@ -9336,9 +9332,9 @@
       <c r="AN32" s="1"/>
       <c r="AO32" s="1"/>
     </row>
-    <row r="33" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" s="35" customFormat="true" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="56" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B33" s="56" t="s">
         <v>148</v>
@@ -9401,9 +9397,9 @@
       <c r="AN33" s="1"/>
       <c r="AO33" s="1"/>
     </row>
-    <row r="34" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" s="35" customFormat="true" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B34" s="56" t="s">
         <v>154</v>
@@ -9466,9 +9462,9 @@
       <c r="AN34" s="1"/>
       <c r="AO34" s="1"/>
     </row>
-    <row r="35" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" s="35" customFormat="true" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="56" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B35" s="56" t="s">
         <v>161</v>
@@ -9531,9 +9527,9 @@
       <c r="AN35" s="1"/>
       <c r="AO35" s="1"/>
     </row>
-    <row r="36" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" s="35" customFormat="true" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="56" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B36" s="56" t="s">
         <v>167</v>
@@ -9596,9 +9592,9 @@
       <c r="AN36" s="1"/>
       <c r="AO36" s="1"/>
     </row>
-    <row r="37" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" s="35" customFormat="true" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="56" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B37" s="56" t="s">
         <v>176</v>
@@ -9661,9 +9657,9 @@
       <c r="AN37" s="1"/>
       <c r="AO37" s="1"/>
     </row>
-    <row r="38" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" s="35" customFormat="true" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="56" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B38" s="56" t="s">
         <v>185</v>
@@ -9726,9 +9722,9 @@
       <c r="AN38" s="1"/>
       <c r="AO38" s="1"/>
     </row>
-    <row r="39" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" s="35" customFormat="true" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="56" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B39" s="56" t="s">
         <v>194</v>
@@ -9791,9 +9787,9 @@
       <c r="AN39" s="1"/>
       <c r="AO39" s="1"/>
     </row>
-    <row r="40" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" s="35" customFormat="true" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="56" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B40" s="56" t="s">
         <v>203</v>
@@ -9856,9 +9852,9 @@
       <c r="AN40" s="1"/>
       <c r="AO40" s="1"/>
     </row>
-    <row r="41" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" s="35" customFormat="true" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="56" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B41" s="56" t="s">
         <v>212</v>
@@ -9922,16 +9918,16 @@
       <c r="AO41" s="1"/>
     </row>
     <row r="42" s="35" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="58"/>
-      <c r="B42" s="58"/>
-      <c r="C42" s="58"/>
-      <c r="D42" s="58"/>
-      <c r="E42" s="58"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="58"/>
-      <c r="H42" s="58"/>
-      <c r="I42" s="58"/>
-      <c r="J42" s="59"/>
+      <c r="A42" s="57"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="57"/>
+      <c r="H42" s="57"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="58"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
@@ -9964,100 +9960,100 @@
       <c r="AO42" s="1"/>
     </row>
     <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="58"/>
-      <c r="B43" s="58"/>
-      <c r="C43" s="58"/>
-      <c r="D43" s="58"/>
-      <c r="E43" s="58"/>
-      <c r="F43" s="58"/>
-      <c r="G43" s="58"/>
-      <c r="H43" s="58"/>
-      <c r="I43" s="58"/>
-      <c r="J43" s="59"/>
+      <c r="A43" s="57"/>
+      <c r="B43" s="57"/>
+      <c r="C43" s="57"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="57"/>
+      <c r="F43" s="57"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="57"/>
+      <c r="I43" s="57"/>
+      <c r="J43" s="58"/>
     </row>
     <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="58"/>
-      <c r="B44" s="58"/>
-      <c r="C44" s="58"/>
-      <c r="D44" s="58"/>
-      <c r="E44" s="58"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="58"/>
-      <c r="H44" s="58"/>
-      <c r="I44" s="58"/>
-      <c r="J44" s="59"/>
+      <c r="A44" s="57"/>
+      <c r="B44" s="57"/>
+      <c r="C44" s="57"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="57"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="57"/>
+      <c r="J44" s="58"/>
     </row>
     <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="58"/>
-      <c r="B45" s="58"/>
-      <c r="C45" s="58"/>
-      <c r="D45" s="58"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="58"/>
-      <c r="H45" s="58"/>
-      <c r="I45" s="58"/>
-      <c r="J45" s="59"/>
+      <c r="A45" s="57"/>
+      <c r="B45" s="57"/>
+      <c r="C45" s="57"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="57"/>
+      <c r="J45" s="58"/>
     </row>
     <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="58"/>
-      <c r="B46" s="58"/>
-      <c r="C46" s="58"/>
-      <c r="D46" s="58"/>
-      <c r="E46" s="58"/>
-      <c r="F46" s="58"/>
-      <c r="G46" s="58"/>
-      <c r="H46" s="58"/>
-      <c r="I46" s="58"/>
-      <c r="J46" s="59"/>
+      <c r="A46" s="57"/>
+      <c r="B46" s="57"/>
+      <c r="C46" s="57"/>
+      <c r="D46" s="57"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="57"/>
+      <c r="G46" s="57"/>
+      <c r="H46" s="57"/>
+      <c r="I46" s="57"/>
+      <c r="J46" s="58"/>
     </row>
     <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="58"/>
-      <c r="B47" s="58"/>
-      <c r="C47" s="58"/>
-      <c r="D47" s="58"/>
-      <c r="E47" s="58"/>
-      <c r="F47" s="58"/>
-      <c r="G47" s="58"/>
-      <c r="H47" s="58"/>
-      <c r="I47" s="58"/>
-      <c r="J47" s="59"/>
+      <c r="A47" s="57"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="57"/>
+      <c r="G47" s="57"/>
+      <c r="H47" s="57"/>
+      <c r="I47" s="57"/>
+      <c r="J47" s="58"/>
     </row>
     <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="58"/>
-      <c r="B48" s="58"/>
-      <c r="C48" s="58"/>
-      <c r="D48" s="58"/>
-      <c r="E48" s="58"/>
-      <c r="F48" s="58"/>
-      <c r="G48" s="58"/>
-      <c r="H48" s="58"/>
-      <c r="I48" s="58"/>
-      <c r="J48" s="59"/>
+      <c r="A48" s="57"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="57"/>
+      <c r="D48" s="57"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="57"/>
+      <c r="G48" s="57"/>
+      <c r="H48" s="57"/>
+      <c r="I48" s="57"/>
+      <c r="J48" s="58"/>
     </row>
     <row r="49" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="58"/>
-      <c r="B49" s="58"/>
-      <c r="C49" s="58"/>
-      <c r="D49" s="58"/>
-      <c r="E49" s="58"/>
-      <c r="F49" s="58"/>
-      <c r="G49" s="58"/>
-      <c r="H49" s="58"/>
-      <c r="I49" s="58"/>
-      <c r="J49" s="59"/>
+      <c r="A49" s="57"/>
+      <c r="B49" s="57"/>
+      <c r="C49" s="57"/>
+      <c r="D49" s="57"/>
+      <c r="E49" s="57"/>
+      <c r="F49" s="57"/>
+      <c r="G49" s="57"/>
+      <c r="H49" s="57"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="58"/>
     </row>
     <row r="50" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="58"/>
-      <c r="B50" s="58"/>
-      <c r="C50" s="58"/>
-      <c r="D50" s="58"/>
-      <c r="E50" s="58"/>
-      <c r="F50" s="58"/>
-      <c r="G50" s="58"/>
-      <c r="H50" s="58"/>
-      <c r="I50" s="58"/>
-      <c r="J50" s="59"/>
+      <c r="A50" s="57"/>
+      <c r="B50" s="57"/>
+      <c r="C50" s="57"/>
+      <c r="D50" s="57"/>
+      <c r="E50" s="57"/>
+      <c r="F50" s="57"/>
+      <c r="G50" s="57"/>
+      <c r="H50" s="57"/>
+      <c r="I50" s="57"/>
+      <c r="J50" s="58"/>
     </row>
     <row r="59" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="54" t="s">
@@ -10166,7 +10162,7 @@
     </row>
     <row r="62" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B62" s="56" t="s">
         <v>120</v>
@@ -10201,7 +10197,7 @@
     </row>
     <row r="63" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B63" s="56" t="s">
         <v>129</v>
@@ -10236,7 +10232,7 @@
     </row>
     <row r="64" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B64" s="56" t="s">
         <v>136</v>
@@ -10271,7 +10267,7 @@
     </row>
     <row r="65" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="56" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B65" s="56" t="s">
         <v>142</v>
@@ -10306,7 +10302,7 @@
     </row>
     <row r="66" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="56" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B66" s="56" t="s">
         <v>148</v>
@@ -10341,7 +10337,7 @@
     </row>
     <row r="67" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B67" s="56" t="s">
         <v>154</v>
@@ -10376,7 +10372,7 @@
     </row>
     <row r="68" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="56" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B68" s="56" t="s">
         <v>161</v>
@@ -10411,7 +10407,7 @@
     </row>
     <row r="69" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="56" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B69" s="56" t="s">
         <v>167</v>
@@ -10446,7 +10442,7 @@
     </row>
     <row r="70" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="56" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B70" s="56" t="s">
         <v>176</v>
@@ -10481,7 +10477,7 @@
     </row>
     <row r="71" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="56" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B71" s="56" t="s">
         <v>185</v>
@@ -10516,7 +10512,7 @@
     </row>
     <row r="72" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="56" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B72" s="56" t="s">
         <v>194</v>
@@ -10551,7 +10547,7 @@
     </row>
     <row r="73" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="56" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B73" s="56" t="s">
         <v>203</v>
@@ -10586,7 +10582,7 @@
     </row>
     <row r="74" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="56" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B74" s="56" t="s">
         <v>212</v>
@@ -10620,7 +10616,7 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I83" s="77"/>
+      <c r="I83" s="76"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -10642,7 +10638,7 @@
   <dimension ref="A1:K42"/>
   <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="78" width="36.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="77" width="36.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="35" width="90.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="35" width="77.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="35" width="65.07"/>
@@ -10651,725 +10647,725 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="79" t="s">
+      <c r="B1" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="79" t="s">
+      <c r="C1" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="79" t="s">
+      <c r="D1" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="79" t="s">
+      <c r="E1" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="80" t="s">
+      <c r="F1" s="79" t="s">
         <v>611</v>
       </c>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="81"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82" t="s">
+      <c r="A2" s="80"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81" t="s">
         <v>612</v>
       </c>
-      <c r="D2" s="82" t="s">
+      <c r="D2" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="82" t="s">
+      <c r="E2" s="81" t="s">
         <v>613</v>
       </c>
-      <c r="F2" s="83"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
     </row>
     <row r="3" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="81"/>
-      <c r="B3" s="82" t="s">
+      <c r="A3" s="80"/>
+      <c r="B3" s="81" t="s">
         <v>614</v>
       </c>
-      <c r="C3" s="84" t="s">
+      <c r="C3" s="83" t="s">
         <v>615</v>
       </c>
-      <c r="D3" s="82" t="s">
+      <c r="D3" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="82" t="s">
+      <c r="E3" s="81" t="s">
         <v>613</v>
       </c>
-      <c r="F3" s="83"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="61"/>
     </row>
     <row r="4" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82" t="s">
+      <c r="A4" s="80"/>
+      <c r="B4" s="81" t="s">
         <v>616</v>
       </c>
-      <c r="C4" s="84" t="s">
+      <c r="C4" s="83" t="s">
         <v>617</v>
       </c>
-      <c r="D4" s="82" t="s">
+      <c r="D4" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="82" t="s">
+      <c r="E4" s="81" t="s">
         <v>618</v>
       </c>
-      <c r="F4" s="83"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
     </row>
     <row r="5" customFormat="false" ht="85.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="81"/>
-      <c r="B5" s="82" t="s">
+      <c r="A5" s="80"/>
+      <c r="B5" s="81" t="s">
         <v>619</v>
       </c>
-      <c r="C5" s="84" t="s">
+      <c r="C5" s="83" t="s">
         <v>615</v>
       </c>
-      <c r="D5" s="82" t="s">
+      <c r="D5" s="81" t="s">
         <v>618</v>
       </c>
-      <c r="E5" s="82" t="s">
+      <c r="E5" s="81" t="s">
         <v>613</v>
       </c>
-      <c r="F5" s="83"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="62"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" s="1" customFormat="true" ht="75.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="81"/>
-      <c r="B6" s="82" t="s">
+      <c r="A6" s="80"/>
+      <c r="B6" s="81" t="s">
         <v>620</v>
       </c>
-      <c r="C6" s="84" t="s">
+      <c r="C6" s="83" t="s">
         <v>621</v>
       </c>
-      <c r="D6" s="82" t="s">
+      <c r="D6" s="81" t="s">
         <v>618</v>
       </c>
-      <c r="E6" s="84" t="s">
+      <c r="E6" s="83" t="s">
         <v>622</v>
       </c>
-      <c r="F6" s="83"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="62"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
     </row>
     <row r="7" s="1" customFormat="true" ht="224.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="81" t="s">
+      <c r="A7" s="80" t="s">
         <v>623</v>
       </c>
-      <c r="B7" s="85" t="s">
+      <c r="B7" s="84" t="s">
         <v>624</v>
       </c>
-      <c r="C7" s="86" t="s">
+      <c r="C7" s="85" t="s">
         <v>625</v>
       </c>
-      <c r="D7" s="86" t="s">
+      <c r="D7" s="85" t="s">
         <v>626</v>
       </c>
-      <c r="E7" s="86" t="s">
+      <c r="E7" s="85" t="s">
         <v>627</v>
       </c>
-      <c r="F7" s="83"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
     </row>
     <row r="8" s="1" customFormat="true" ht="113.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="81" t="s">
+      <c r="A8" s="80" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="85" t="s">
+      <c r="B8" s="84" t="s">
         <v>628</v>
       </c>
-      <c r="C8" s="86" t="s">
+      <c r="C8" s="85" t="s">
         <v>629</v>
       </c>
-      <c r="D8" s="86" t="s">
+      <c r="D8" s="85" t="s">
         <v>626</v>
       </c>
-      <c r="E8" s="86" t="s">
+      <c r="E8" s="85" t="s">
         <v>630</v>
       </c>
-      <c r="F8" s="83"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="62"/>
-      <c r="K8" s="62"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="61"/>
     </row>
     <row r="9" s="1" customFormat="true" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="81" t="s">
+      <c r="A9" s="80" t="s">
         <v>74</v>
       </c>
-      <c r="B9" s="85" t="s">
+      <c r="B9" s="84" t="s">
         <v>631</v>
       </c>
-      <c r="C9" s="86" t="s">
+      <c r="C9" s="85" t="s">
         <v>625</v>
       </c>
-      <c r="D9" s="86" t="s">
+      <c r="D9" s="85" t="s">
         <v>630</v>
       </c>
-      <c r="E9" s="86" t="s">
+      <c r="E9" s="85" t="s">
         <v>632</v>
       </c>
-      <c r="F9" s="83"/>
-      <c r="G9" s="62"/>
-      <c r="H9" s="62"/>
-      <c r="I9" s="62"/>
-      <c r="J9" s="62"/>
-      <c r="K9" s="62"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="61"/>
+      <c r="K9" s="61"/>
     </row>
     <row r="10" s="1" customFormat="true" ht="106.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="87" t="s">
+      <c r="A10" s="86" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="88" t="s">
+      <c r="B10" s="87" t="s">
         <v>633</v>
       </c>
-      <c r="C10" s="89" t="s">
+      <c r="C10" s="88" t="s">
         <v>634</v>
       </c>
-      <c r="D10" s="89" t="s">
+      <c r="D10" s="88" t="s">
         <v>626</v>
       </c>
-      <c r="E10" s="89" t="s">
+      <c r="E10" s="88" t="s">
         <v>635</v>
       </c>
       <c r="F10" s="24"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="62"/>
-      <c r="J10" s="62"/>
-      <c r="K10" s="62"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
     </row>
     <row r="11" customFormat="false" ht="242.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="90" t="s">
+      <c r="A11" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="91" t="s">
+      <c r="B11" s="90" t="s">
         <v>636</v>
       </c>
-      <c r="C11" s="92" t="s">
+      <c r="C11" s="91" t="s">
         <v>625</v>
       </c>
-      <c r="D11" s="92" t="s">
+      <c r="D11" s="91" t="s">
         <v>635</v>
       </c>
-      <c r="E11" s="92" t="s">
+      <c r="E11" s="91" t="s">
         <v>637</v>
       </c>
-      <c r="F11" s="93"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="62"/>
-      <c r="I11" s="62"/>
-      <c r="J11" s="62"/>
-      <c r="K11" s="62"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="61"/>
+      <c r="K11" s="61"/>
     </row>
     <row r="12" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="90" t="s">
+      <c r="A12" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="92" t="s">
+      <c r="B12" s="91" t="s">
         <v>638</v>
       </c>
-      <c r="C12" s="92" t="s">
+      <c r="C12" s="91" t="s">
         <v>639</v>
       </c>
-      <c r="D12" s="92" t="s">
+      <c r="D12" s="91" t="s">
         <v>640</v>
       </c>
-      <c r="E12" s="92"/>
-      <c r="F12" s="94" t="s">
+      <c r="E12" s="91"/>
+      <c r="F12" s="93" t="s">
         <v>641</v>
       </c>
-      <c r="G12" s="62"/>
-      <c r="H12" s="62"/>
-      <c r="I12" s="62"/>
-      <c r="J12" s="62"/>
-      <c r="K12" s="62"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="61"/>
     </row>
     <row r="13" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="90" t="s">
+      <c r="A13" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="92" t="s">
+      <c r="B13" s="91" t="s">
         <v>642</v>
       </c>
-      <c r="C13" s="92" t="s">
+      <c r="C13" s="91" t="s">
         <v>643</v>
       </c>
-      <c r="D13" s="92" t="s">
+      <c r="D13" s="91" t="s">
         <v>644</v>
       </c>
-      <c r="E13" s="92"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="62"/>
-      <c r="K13" s="62"/>
+      <c r="E13" s="91"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="61"/>
     </row>
     <row r="14" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="95"/>
-      <c r="B14" s="96"/>
-      <c r="C14" s="96"/>
-      <c r="D14" s="96"/>
-      <c r="E14" s="96"/>
-      <c r="F14" s="97"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="62"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="96"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="61"/>
     </row>
     <row r="15" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="98"/>
-      <c r="B15" s="99"/>
-      <c r="C15" s="99"/>
-      <c r="D15" s="99"/>
-      <c r="E15" s="99"/>
-      <c r="F15" s="100"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="62"/>
-      <c r="I15" s="62"/>
-      <c r="J15" s="62"/>
-      <c r="K15" s="62"/>
+      <c r="A15" s="97"/>
+      <c r="B15" s="98"/>
+      <c r="C15" s="98"/>
+      <c r="D15" s="98"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="61"/>
     </row>
     <row r="16" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="87" t="s">
+      <c r="A16" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="89" t="s">
+      <c r="B16" s="88" t="s">
         <v>645</v>
       </c>
-      <c r="C16" s="89" t="s">
+      <c r="C16" s="88" t="s">
         <v>629</v>
       </c>
-      <c r="D16" s="89" t="s">
+      <c r="D16" s="88" t="s">
         <v>646</v>
       </c>
-      <c r="E16" s="89" t="s">
+      <c r="E16" s="88" t="s">
         <v>647</v>
       </c>
-      <c r="F16" s="101"/>
-      <c r="G16" s="62"/>
-      <c r="H16" s="62"/>
-      <c r="I16" s="62"/>
-      <c r="J16" s="62"/>
-      <c r="K16" s="62"/>
+      <c r="F16" s="100"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="61"/>
+      <c r="K16" s="61"/>
     </row>
     <row r="17" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="90" t="s">
+      <c r="A17" s="89" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="92" t="s">
+      <c r="B17" s="91" t="s">
         <v>648</v>
       </c>
-      <c r="C17" s="92" t="s">
+      <c r="C17" s="91" t="s">
         <v>625</v>
       </c>
-      <c r="D17" s="92" t="s">
+      <c r="D17" s="91" t="s">
         <v>647</v>
       </c>
-      <c r="E17" s="92" t="s">
+      <c r="E17" s="91" t="s">
         <v>649</v>
       </c>
-      <c r="F17" s="94"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="62"/>
+      <c r="F17" s="93"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="61"/>
     </row>
     <row r="18" customFormat="false" ht="184.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="102" t="s">
+      <c r="A18" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="103" t="s">
+      <c r="B18" s="102" t="s">
         <v>650</v>
       </c>
-      <c r="C18" s="103" t="s">
+      <c r="C18" s="102" t="s">
         <v>639</v>
       </c>
-      <c r="D18" s="103" t="s">
+      <c r="D18" s="102" t="s">
         <v>651</v>
       </c>
-      <c r="E18" s="103"/>
-      <c r="F18" s="104" t="s">
+      <c r="E18" s="102"/>
+      <c r="F18" s="103" t="s">
         <v>652</v>
       </c>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="61"/>
+      <c r="K18" s="61"/>
     </row>
     <row r="19" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="95" t="s">
+      <c r="A19" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="96" t="s">
+      <c r="B19" s="95" t="s">
         <v>653</v>
       </c>
-      <c r="C19" s="96" t="s">
+      <c r="C19" s="95" t="s">
         <v>643</v>
       </c>
-      <c r="D19" s="96" t="s">
+      <c r="D19" s="95" t="s">
         <v>654</v>
       </c>
-      <c r="E19" s="96"/>
-      <c r="F19" s="97"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="96"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="61"/>
+      <c r="K19" s="61"/>
     </row>
     <row r="20" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="95"/>
-      <c r="B20" s="96"/>
-      <c r="C20" s="96"/>
-      <c r="D20" s="96"/>
-      <c r="E20" s="96"/>
-      <c r="F20" s="97"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62"/>
+      <c r="A20" s="94"/>
+      <c r="B20" s="95"/>
+      <c r="C20" s="95"/>
+      <c r="D20" s="95"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="96"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="61"/>
     </row>
     <row r="21" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="105"/>
-      <c r="B21" s="106"/>
-      <c r="C21" s="106"/>
-      <c r="D21" s="106"/>
-      <c r="E21" s="106"/>
-      <c r="F21" s="107"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="62"/>
+      <c r="A21" s="104"/>
+      <c r="B21" s="105"/>
+      <c r="C21" s="105"/>
+      <c r="D21" s="105"/>
+      <c r="E21" s="105"/>
+      <c r="F21" s="106"/>
+      <c r="G21" s="61"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="61"/>
+      <c r="K21" s="61"/>
     </row>
     <row r="22" customFormat="false" ht="172.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="87" t="s">
+      <c r="A22" s="86" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="88" t="s">
+      <c r="B22" s="87" t="s">
         <v>655</v>
       </c>
-      <c r="C22" s="89" t="s">
+      <c r="C22" s="88" t="s">
         <v>634</v>
       </c>
-      <c r="D22" s="89" t="s">
+      <c r="D22" s="88" t="s">
         <v>626</v>
       </c>
-      <c r="E22" s="89" t="s">
+      <c r="E22" s="88" t="s">
         <v>656</v>
       </c>
       <c r="F22" s="24"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62"/>
-      <c r="K22" s="62"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="61"/>
+      <c r="K22" s="61"/>
     </row>
     <row r="23" customFormat="false" ht="256.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="90" t="s">
+      <c r="A23" s="89" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="91" t="s">
+      <c r="B23" s="90" t="s">
         <v>657</v>
       </c>
-      <c r="C23" s="92" t="s">
+      <c r="C23" s="91" t="s">
         <v>625</v>
       </c>
-      <c r="D23" s="92" t="s">
+      <c r="D23" s="91" t="s">
         <v>656</v>
       </c>
-      <c r="E23" s="92" t="s">
+      <c r="E23" s="91" t="s">
         <v>658</v>
       </c>
-      <c r="F23" s="93"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="62"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="61"/>
+      <c r="K23" s="61"/>
     </row>
     <row r="24" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="102" t="s">
+      <c r="A24" s="101" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="103" t="s">
+      <c r="B24" s="102" t="s">
         <v>659</v>
       </c>
-      <c r="C24" s="103" t="s">
+      <c r="C24" s="102" t="s">
         <v>639</v>
       </c>
-      <c r="D24" s="103" t="s">
+      <c r="D24" s="102" t="s">
         <v>660</v>
       </c>
-      <c r="E24" s="103"/>
-      <c r="F24" s="104" t="s">
+      <c r="E24" s="102"/>
+      <c r="F24" s="103" t="s">
         <v>661</v>
       </c>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="62"/>
+      <c r="G24" s="61"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="61"/>
+      <c r="K24" s="61"/>
     </row>
     <row r="25" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="95" t="s">
+      <c r="A25" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="96" t="s">
+      <c r="B25" s="95" t="s">
         <v>662</v>
       </c>
-      <c r="C25" s="96" t="s">
+      <c r="C25" s="95" t="s">
         <v>643</v>
       </c>
-      <c r="D25" s="96" t="s">
+      <c r="D25" s="95" t="s">
         <v>663</v>
       </c>
-      <c r="E25" s="96"/>
-      <c r="F25" s="97"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="62"/>
+      <c r="E25" s="95"/>
+      <c r="F25" s="96"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="61"/>
+      <c r="K25" s="61"/>
     </row>
     <row r="26" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="95"/>
-      <c r="B26" s="96"/>
-      <c r="C26" s="96"/>
-      <c r="D26" s="96"/>
-      <c r="E26" s="96"/>
-      <c r="F26" s="97"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="62"/>
-      <c r="K26" s="62"/>
+      <c r="A26" s="94"/>
+      <c r="B26" s="95"/>
+      <c r="C26" s="95"/>
+      <c r="D26" s="95"/>
+      <c r="E26" s="95"/>
+      <c r="F26" s="96"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="61"/>
+      <c r="K26" s="61"/>
     </row>
     <row r="27" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="98"/>
-      <c r="B27" s="99"/>
-      <c r="C27" s="99"/>
-      <c r="D27" s="99"/>
-      <c r="E27" s="99"/>
-      <c r="F27" s="100"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="62"/>
+      <c r="A27" s="97"/>
+      <c r="B27" s="98"/>
+      <c r="C27" s="98"/>
+      <c r="D27" s="98"/>
+      <c r="E27" s="98"/>
+      <c r="F27" s="99"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="61"/>
+      <c r="J27" s="61"/>
+      <c r="K27" s="61"/>
     </row>
     <row r="28" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="87" t="s">
+      <c r="A28" s="86" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="89" t="s">
+      <c r="B28" s="88" t="s">
         <v>664</v>
       </c>
-      <c r="C28" s="89" t="s">
+      <c r="C28" s="88" t="s">
         <v>629</v>
       </c>
-      <c r="D28" s="89" t="s">
+      <c r="D28" s="88" t="s">
         <v>665</v>
       </c>
-      <c r="E28" s="89" t="s">
+      <c r="E28" s="88" t="s">
         <v>666</v>
       </c>
-      <c r="F28" s="101"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="62"/>
+      <c r="F28" s="100"/>
+      <c r="G28" s="61"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="61"/>
+      <c r="K28" s="61"/>
     </row>
     <row r="29" customFormat="false" ht="195.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="90" t="s">
+      <c r="A29" s="89" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="92" t="s">
+      <c r="B29" s="91" t="s">
         <v>667</v>
       </c>
-      <c r="C29" s="92" t="s">
+      <c r="C29" s="91" t="s">
         <v>625</v>
       </c>
-      <c r="D29" s="92" t="s">
+      <c r="D29" s="91" t="s">
         <v>666</v>
       </c>
-      <c r="E29" s="92" t="s">
+      <c r="E29" s="91" t="s">
         <v>668</v>
       </c>
-      <c r="F29" s="94"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="62"/>
-      <c r="K29" s="62"/>
+      <c r="F29" s="93"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="61"/>
+      <c r="J29" s="61"/>
+      <c r="K29" s="61"/>
     </row>
     <row r="30" customFormat="false" ht="199" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="102" t="s">
+      <c r="A30" s="101" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="103" t="s">
+      <c r="B30" s="102" t="s">
         <v>669</v>
       </c>
-      <c r="C30" s="103" t="s">
+      <c r="C30" s="102" t="s">
         <v>639</v>
       </c>
-      <c r="D30" s="103" t="s">
+      <c r="D30" s="102" t="s">
         <v>670</v>
       </c>
-      <c r="E30" s="103"/>
-      <c r="F30" s="104" t="s">
+      <c r="E30" s="102"/>
+      <c r="F30" s="103" t="s">
         <v>671</v>
       </c>
-      <c r="G30" s="62"/>
-      <c r="H30" s="62"/>
-      <c r="I30" s="62"/>
-      <c r="J30" s="62"/>
-      <c r="K30" s="62"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="61"/>
+      <c r="J30" s="61"/>
+      <c r="K30" s="61"/>
     </row>
     <row r="31" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="95" t="s">
+      <c r="A31" s="94" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="96" t="s">
+      <c r="B31" s="95" t="s">
         <v>672</v>
       </c>
-      <c r="C31" s="96" t="s">
+      <c r="C31" s="95" t="s">
         <v>643</v>
       </c>
-      <c r="D31" s="96" t="s">
+      <c r="D31" s="95" t="s">
         <v>673</v>
       </c>
-      <c r="E31" s="96"/>
-      <c r="F31" s="97"/>
-      <c r="G31" s="62"/>
-      <c r="H31" s="62"/>
-      <c r="I31" s="62"/>
-      <c r="J31" s="62"/>
-      <c r="K31" s="62"/>
+      <c r="E31" s="95"/>
+      <c r="F31" s="96"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="61"/>
+      <c r="K31" s="61"/>
     </row>
     <row r="32" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="95"/>
-      <c r="B32" s="96"/>
-      <c r="C32" s="96"/>
-      <c r="D32" s="96"/>
-      <c r="E32" s="96"/>
-      <c r="F32" s="97"/>
-      <c r="G32" s="62"/>
-      <c r="H32" s="62"/>
-      <c r="I32" s="62"/>
-      <c r="J32" s="62"/>
-      <c r="K32" s="62"/>
+      <c r="A32" s="94"/>
+      <c r="B32" s="95"/>
+      <c r="C32" s="95"/>
+      <c r="D32" s="95"/>
+      <c r="E32" s="95"/>
+      <c r="F32" s="96"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="61"/>
+      <c r="J32" s="61"/>
+      <c r="K32" s="61"/>
     </row>
     <row r="33" customFormat="false" ht="149.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="98"/>
-      <c r="B33" s="108"/>
-      <c r="C33" s="108"/>
-      <c r="D33" s="108"/>
-      <c r="E33" s="108"/>
-      <c r="F33" s="109"/>
-      <c r="G33" s="62"/>
-      <c r="H33" s="62"/>
-      <c r="I33" s="62"/>
-      <c r="J33" s="62"/>
-      <c r="K33" s="62"/>
+      <c r="A33" s="97"/>
+      <c r="B33" s="107"/>
+      <c r="C33" s="107"/>
+      <c r="D33" s="107"/>
+      <c r="E33" s="107"/>
+      <c r="F33" s="108"/>
+      <c r="G33" s="61"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="61"/>
+      <c r="J33" s="61"/>
+      <c r="K33" s="61"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="62"/>
-      <c r="H34" s="62"/>
-      <c r="I34" s="62"/>
-      <c r="J34" s="62"/>
-      <c r="K34" s="62"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="61"/>
+      <c r="J34" s="61"/>
+      <c r="K34" s="61"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G35" s="62"/>
-      <c r="H35" s="62"/>
-      <c r="I35" s="62"/>
-      <c r="J35" s="62"/>
-      <c r="K35" s="62"/>
+      <c r="G35" s="61"/>
+      <c r="H35" s="61"/>
+      <c r="I35" s="61"/>
+      <c r="J35" s="61"/>
+      <c r="K35" s="61"/>
     </row>
     <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G36" s="62"/>
-      <c r="H36" s="62"/>
-      <c r="I36" s="62"/>
-      <c r="J36" s="62"/>
-      <c r="K36" s="62"/>
+      <c r="G36" s="61"/>
+      <c r="H36" s="61"/>
+      <c r="I36" s="61"/>
+      <c r="J36" s="61"/>
+      <c r="K36" s="61"/>
     </row>
     <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G37" s="62"/>
-      <c r="H37" s="62"/>
-      <c r="I37" s="62"/>
-      <c r="J37" s="62"/>
-      <c r="K37" s="62"/>
+      <c r="G37" s="61"/>
+      <c r="H37" s="61"/>
+      <c r="I37" s="61"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="61"/>
     </row>
     <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G38" s="62"/>
-      <c r="H38" s="62"/>
-      <c r="I38" s="62"/>
-      <c r="J38" s="62"/>
-      <c r="K38" s="62"/>
+      <c r="G38" s="61"/>
+      <c r="H38" s="61"/>
+      <c r="I38" s="61"/>
+      <c r="J38" s="61"/>
+      <c r="K38" s="61"/>
     </row>
     <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G39" s="62"/>
-      <c r="H39" s="62"/>
-      <c r="I39" s="62"/>
-      <c r="J39" s="62"/>
-      <c r="K39" s="62"/>
+      <c r="G39" s="61"/>
+      <c r="H39" s="61"/>
+      <c r="I39" s="61"/>
+      <c r="J39" s="61"/>
+      <c r="K39" s="61"/>
     </row>
     <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G40" s="62"/>
-      <c r="H40" s="62"/>
-      <c r="I40" s="62"/>
-      <c r="J40" s="62"/>
-      <c r="K40" s="62"/>
+      <c r="G40" s="61"/>
+      <c r="H40" s="61"/>
+      <c r="I40" s="61"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="61"/>
     </row>
     <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G41" s="62"/>
-      <c r="H41" s="62"/>
-      <c r="I41" s="62"/>
-      <c r="J41" s="62"/>
-      <c r="K41" s="62"/>
+      <c r="G41" s="61"/>
+      <c r="H41" s="61"/>
+      <c r="I41" s="61"/>
+      <c r="J41" s="61"/>
+      <c r="K41" s="61"/>
     </row>
     <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G42" s="62"/>
-      <c r="H42" s="62"/>
-      <c r="I42" s="62"/>
-      <c r="J42" s="62"/>
-      <c r="K42" s="62"/>
+      <c r="G42" s="61"/>
+      <c r="H42" s="61"/>
+      <c r="I42" s="61"/>
+      <c r="J42" s="61"/>
+      <c r="K42" s="61"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -11403,32 +11399,32 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="19.47"/>
   </cols>
   <sheetData>
-    <row r="1" s="111" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="64" t="s">
+    <row r="1" s="110" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="64" t="s">
+      <c r="B1" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="C1" s="64" t="s">
         <v>674</v>
       </c>
-      <c r="D1" s="65" t="s">
+      <c r="D1" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="64" t="s">
         <v>675</v>
       </c>
-      <c r="F1" s="65" t="s">
+      <c r="F1" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="65" t="s">
+      <c r="G1" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="65" t="s">
+      <c r="H1" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="109" t="s">
         <v>58</v>
       </c>
       <c r="XFC1" s="1"/>
@@ -11825,7 +11821,7 @@
       <c r="J14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="112" t="s">
+      <c r="A15" s="111" t="s">
         <v>388</v>
       </c>
       <c r="B15" s="48" t="n">
@@ -11916,7 +11912,7 @@
       <c r="H19" s="1"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="24" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="54" t="s">
         <v>91</v>
       </c>
@@ -11958,31 +11954,31 @@
       <c r="B25" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="57" t="s">
+      <c r="C25" s="42" t="s">
         <v>687</v>
       </c>
-      <c r="D25" s="57" t="s">
+      <c r="D25" s="42" t="s">
         <v>688</v>
       </c>
-      <c r="E25" s="57" t="s">
+      <c r="E25" s="42" t="s">
         <v>687</v>
       </c>
-      <c r="F25" s="57" t="s">
+      <c r="F25" s="42" t="s">
         <v>689</v>
       </c>
-      <c r="G25" s="57" t="s">
+      <c r="G25" s="42" t="s">
         <v>690</v>
       </c>
-      <c r="H25" s="57" t="s">
+      <c r="H25" s="42" t="s">
         <v>691</v>
       </c>
-      <c r="I25" s="57" t="s">
+      <c r="I25" s="42" t="s">
         <v>692</v>
       </c>
-      <c r="J25" s="57" t="s">
+      <c r="J25" s="42" t="s">
         <v>693</v>
       </c>
-      <c r="K25" s="57" t="s">
+      <c r="K25" s="42" t="s">
         <v>694</v>
       </c>
     </row>
@@ -11993,31 +11989,31 @@
       <c r="B26" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="C26" s="57" t="s">
+      <c r="C26" s="42" t="s">
         <v>695</v>
       </c>
-      <c r="D26" s="57" t="s">
+      <c r="D26" s="42" t="s">
         <v>696</v>
       </c>
-      <c r="E26" s="57" t="s">
+      <c r="E26" s="42" t="s">
         <v>697</v>
       </c>
-      <c r="F26" s="57" t="s">
+      <c r="F26" s="42" t="s">
         <v>698</v>
       </c>
-      <c r="G26" s="57" t="s">
+      <c r="G26" s="42" t="s">
         <v>699</v>
       </c>
-      <c r="H26" s="57" t="s">
+      <c r="H26" s="42" t="s">
         <v>700</v>
       </c>
-      <c r="I26" s="57" t="s">
+      <c r="I26" s="42" t="s">
         <v>701</v>
       </c>
-      <c r="J26" s="57" t="s">
+      <c r="J26" s="42" t="s">
         <v>702</v>
       </c>
-      <c r="K26" s="57" t="s">
+      <c r="K26" s="42" t="s">
         <v>703</v>
       </c>
     </row>
@@ -12028,31 +12024,31 @@
       <c r="B27" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="C27" s="57" t="s">
+      <c r="C27" s="42" t="s">
         <v>704</v>
       </c>
-      <c r="D27" s="57" t="s">
+      <c r="D27" s="42" t="s">
         <v>705</v>
       </c>
-      <c r="E27" s="57" t="s">
+      <c r="E27" s="42" t="s">
         <v>704</v>
       </c>
-      <c r="F27" s="57" t="s">
+      <c r="F27" s="42" t="s">
         <v>706</v>
       </c>
-      <c r="G27" s="57" t="s">
+      <c r="G27" s="42" t="s">
         <v>707</v>
       </c>
-      <c r="H27" s="57" t="s">
+      <c r="H27" s="42" t="s">
         <v>708</v>
       </c>
-      <c r="I27" s="57" t="s">
+      <c r="I27" s="42" t="s">
         <v>709</v>
       </c>
-      <c r="J27" s="57" t="s">
+      <c r="J27" s="42" t="s">
         <v>710</v>
       </c>
-      <c r="K27" s="57" t="s">
+      <c r="K27" s="42" t="s">
         <v>711</v>
       </c>
     </row>
@@ -12063,31 +12059,31 @@
       <c r="B28" s="56" t="s">
         <v>129</v>
       </c>
-      <c r="C28" s="57" t="s">
+      <c r="C28" s="42" t="s">
         <v>712</v>
       </c>
-      <c r="D28" s="57" t="s">
+      <c r="D28" s="42" t="s">
         <v>713</v>
       </c>
-      <c r="E28" s="57" t="s">
+      <c r="E28" s="42" t="s">
         <v>712</v>
       </c>
-      <c r="F28" s="57" t="s">
+      <c r="F28" s="42" t="s">
         <v>714</v>
       </c>
-      <c r="G28" s="57" t="s">
+      <c r="G28" s="42" t="s">
         <v>713</v>
       </c>
-      <c r="H28" s="57" t="s">
+      <c r="H28" s="42" t="s">
         <v>712</v>
       </c>
-      <c r="I28" s="57" t="s">
+      <c r="I28" s="42" t="s">
         <v>714</v>
       </c>
-      <c r="J28" s="57" t="s">
+      <c r="J28" s="42" t="s">
         <v>715</v>
       </c>
-      <c r="K28" s="57" t="s">
+      <c r="K28" s="42" t="s">
         <v>716</v>
       </c>
     </row>
@@ -12098,31 +12094,31 @@
       <c r="B29" s="56" t="s">
         <v>136</v>
       </c>
-      <c r="C29" s="57" t="s">
+      <c r="C29" s="42" t="s">
         <v>717</v>
       </c>
-      <c r="D29" s="57" t="s">
+      <c r="D29" s="42" t="s">
         <v>718</v>
       </c>
-      <c r="E29" s="57" t="s">
+      <c r="E29" s="42" t="s">
         <v>717</v>
       </c>
-      <c r="F29" s="57" t="s">
+      <c r="F29" s="42" t="s">
         <v>719</v>
       </c>
-      <c r="G29" s="57" t="s">
+      <c r="G29" s="42" t="s">
         <v>718</v>
       </c>
-      <c r="H29" s="57" t="s">
+      <c r="H29" s="42" t="s">
         <v>717</v>
       </c>
-      <c r="I29" s="57" t="s">
+      <c r="I29" s="42" t="s">
         <v>719</v>
       </c>
-      <c r="J29" s="57" t="s">
+      <c r="J29" s="42" t="s">
         <v>720</v>
       </c>
-      <c r="K29" s="57" t="s">
+      <c r="K29" s="42" t="s">
         <v>721</v>
       </c>
     </row>
@@ -12133,31 +12129,31 @@
       <c r="B30" s="56" t="s">
         <v>142</v>
       </c>
-      <c r="C30" s="57" t="s">
+      <c r="C30" s="42" t="s">
         <v>722</v>
       </c>
-      <c r="D30" s="57" t="s">
+      <c r="D30" s="42" t="s">
         <v>723</v>
       </c>
-      <c r="E30" s="57" t="s">
+      <c r="E30" s="42" t="s">
         <v>724</v>
       </c>
-      <c r="F30" s="57" t="s">
+      <c r="F30" s="42" t="s">
         <v>725</v>
       </c>
-      <c r="G30" s="57" t="s">
+      <c r="G30" s="42" t="s">
         <v>723</v>
       </c>
-      <c r="H30" s="57" t="s">
+      <c r="H30" s="42" t="s">
         <v>722</v>
       </c>
-      <c r="I30" s="57" t="s">
+      <c r="I30" s="42" t="s">
         <v>725</v>
       </c>
-      <c r="J30" s="57" t="s">
+      <c r="J30" s="42" t="s">
         <v>726</v>
       </c>
-      <c r="K30" s="57" t="s">
+      <c r="K30" s="42" t="s">
         <v>727</v>
       </c>
     </row>
@@ -12168,31 +12164,31 @@
       <c r="B31" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="C31" s="57" t="s">
+      <c r="C31" s="42" t="s">
         <v>728</v>
       </c>
-      <c r="D31" s="57" t="s">
+      <c r="D31" s="42" t="s">
         <v>729</v>
       </c>
-      <c r="E31" s="57" t="s">
+      <c r="E31" s="42" t="s">
         <v>728</v>
       </c>
-      <c r="F31" s="57" t="s">
+      <c r="F31" s="42" t="s">
         <v>730</v>
       </c>
-      <c r="G31" s="57" t="s">
+      <c r="G31" s="42" t="s">
         <v>729</v>
       </c>
-      <c r="H31" s="57" t="s">
+      <c r="H31" s="42" t="s">
         <v>728</v>
       </c>
-      <c r="I31" s="57" t="s">
+      <c r="I31" s="42" t="s">
         <v>730</v>
       </c>
-      <c r="J31" s="57" t="s">
+      <c r="J31" s="42" t="s">
         <v>731</v>
       </c>
-      <c r="K31" s="57" t="s">
+      <c r="K31" s="42" t="s">
         <v>732</v>
       </c>
     </row>
@@ -12203,31 +12199,31 @@
       <c r="B32" s="56" t="s">
         <v>154</v>
       </c>
-      <c r="C32" s="57" t="s">
+      <c r="C32" s="42" t="s">
         <v>733</v>
       </c>
-      <c r="D32" s="57" t="s">
+      <c r="D32" s="42" t="s">
         <v>734</v>
       </c>
-      <c r="E32" s="57" t="s">
+      <c r="E32" s="42" t="s">
         <v>733</v>
       </c>
-      <c r="F32" s="57" t="s">
+      <c r="F32" s="42" t="s">
         <v>735</v>
       </c>
-      <c r="G32" s="57" t="s">
+      <c r="G32" s="42" t="s">
         <v>736</v>
       </c>
-      <c r="H32" s="57" t="s">
+      <c r="H32" s="42" t="s">
         <v>733</v>
       </c>
-      <c r="I32" s="57" t="s">
+      <c r="I32" s="42" t="s">
         <v>735</v>
       </c>
-      <c r="J32" s="57" t="s">
+      <c r="J32" s="42" t="s">
         <v>737</v>
       </c>
-      <c r="K32" s="57" t="s">
+      <c r="K32" s="42" t="s">
         <v>738</v>
       </c>
     </row>
@@ -12238,31 +12234,31 @@
       <c r="B33" s="56" t="s">
         <v>161</v>
       </c>
-      <c r="C33" s="57" t="s">
+      <c r="C33" s="42" t="s">
         <v>739</v>
       </c>
-      <c r="D33" s="57" t="s">
+      <c r="D33" s="42" t="s">
         <v>740</v>
       </c>
-      <c r="E33" s="57" t="s">
+      <c r="E33" s="42" t="s">
         <v>739</v>
       </c>
-      <c r="F33" s="57" t="s">
+      <c r="F33" s="42" t="s">
         <v>741</v>
       </c>
-      <c r="G33" s="57" t="s">
+      <c r="G33" s="42" t="s">
         <v>740</v>
       </c>
-      <c r="H33" s="57" t="s">
+      <c r="H33" s="42" t="s">
         <v>739</v>
       </c>
-      <c r="I33" s="57" t="s">
+      <c r="I33" s="42" t="s">
         <v>741</v>
       </c>
-      <c r="J33" s="57" t="s">
+      <c r="J33" s="42" t="s">
         <v>742</v>
       </c>
-      <c r="K33" s="57" t="s">
+      <c r="K33" s="42" t="s">
         <v>743</v>
       </c>
     </row>
@@ -12273,31 +12269,31 @@
       <c r="B34" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="C34" s="57" t="s">
+      <c r="C34" s="42" t="s">
         <v>744</v>
       </c>
-      <c r="D34" s="57" t="s">
+      <c r="D34" s="42" t="s">
         <v>745</v>
       </c>
-      <c r="E34" s="57" t="s">
+      <c r="E34" s="42" t="s">
         <v>744</v>
       </c>
-      <c r="F34" s="57" t="s">
+      <c r="F34" s="42" t="s">
         <v>746</v>
       </c>
-      <c r="G34" s="57" t="s">
+      <c r="G34" s="42" t="s">
         <v>747</v>
       </c>
-      <c r="H34" s="57" t="s">
+      <c r="H34" s="42" t="s">
         <v>748</v>
       </c>
-      <c r="I34" s="57" t="s">
+      <c r="I34" s="42" t="s">
         <v>749</v>
       </c>
-      <c r="J34" s="57" t="s">
+      <c r="J34" s="42" t="s">
         <v>750</v>
       </c>
-      <c r="K34" s="57" t="s">
+      <c r="K34" s="42" t="s">
         <v>751</v>
       </c>
     </row>
@@ -12308,31 +12304,31 @@
       <c r="B35" s="56" t="s">
         <v>176</v>
       </c>
-      <c r="C35" s="57" t="s">
+      <c r="C35" s="42" t="s">
         <v>752</v>
       </c>
-      <c r="D35" s="57" t="s">
+      <c r="D35" s="42" t="s">
         <v>753</v>
       </c>
-      <c r="E35" s="57" t="s">
+      <c r="E35" s="42" t="s">
         <v>752</v>
       </c>
-      <c r="F35" s="57" t="s">
+      <c r="F35" s="42" t="s">
         <v>754</v>
       </c>
-      <c r="G35" s="57" t="s">
+      <c r="G35" s="42" t="s">
         <v>755</v>
       </c>
-      <c r="H35" s="57" t="s">
+      <c r="H35" s="42" t="s">
         <v>756</v>
       </c>
-      <c r="I35" s="57" t="s">
+      <c r="I35" s="42" t="s">
         <v>757</v>
       </c>
-      <c r="J35" s="57" t="s">
+      <c r="J35" s="42" t="s">
         <v>758</v>
       </c>
-      <c r="K35" s="57" t="s">
+      <c r="K35" s="42" t="s">
         <v>759</v>
       </c>
     </row>
@@ -12343,31 +12339,31 @@
       <c r="B36" s="56" t="s">
         <v>185</v>
       </c>
-      <c r="C36" s="57" t="s">
+      <c r="C36" s="42" t="s">
         <v>760</v>
       </c>
-      <c r="D36" s="57" t="s">
+      <c r="D36" s="42" t="s">
         <v>761</v>
       </c>
-      <c r="E36" s="57" t="s">
+      <c r="E36" s="42" t="s">
         <v>760</v>
       </c>
-      <c r="F36" s="57" t="s">
+      <c r="F36" s="42" t="s">
         <v>762</v>
       </c>
-      <c r="G36" s="57" t="s">
+      <c r="G36" s="42" t="s">
         <v>763</v>
       </c>
-      <c r="H36" s="57" t="s">
+      <c r="H36" s="42" t="s">
         <v>764</v>
       </c>
-      <c r="I36" s="57" t="s">
+      <c r="I36" s="42" t="s">
         <v>765</v>
       </c>
-      <c r="J36" s="57" t="s">
+      <c r="J36" s="42" t="s">
         <v>766</v>
       </c>
-      <c r="K36" s="57" t="s">
+      <c r="K36" s="42" t="s">
         <v>767</v>
       </c>
     </row>
@@ -12378,219 +12374,219 @@
       <c r="B37" s="56" t="s">
         <v>194</v>
       </c>
-      <c r="C37" s="57" t="s">
+      <c r="C37" s="42" t="s">
         <v>768</v>
       </c>
-      <c r="D37" s="57" t="s">
+      <c r="D37" s="42" t="s">
         <v>769</v>
       </c>
-      <c r="E37" s="57" t="s">
+      <c r="E37" s="42" t="s">
         <v>768</v>
       </c>
-      <c r="F37" s="57" t="s">
+      <c r="F37" s="42" t="s">
         <v>770</v>
       </c>
-      <c r="G37" s="57" t="s">
+      <c r="G37" s="42" t="s">
         <v>771</v>
       </c>
-      <c r="H37" s="57" t="s">
+      <c r="H37" s="42" t="s">
         <v>772</v>
       </c>
-      <c r="I37" s="57" t="s">
+      <c r="I37" s="42" t="s">
         <v>773</v>
       </c>
-      <c r="J37" s="57" t="s">
+      <c r="J37" s="42" t="s">
         <v>774</v>
       </c>
-      <c r="K37" s="57" t="s">
+      <c r="K37" s="42" t="s">
         <v>775</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="56" t="n">
         <v>18</v>
       </c>
       <c r="B38" s="56" t="s">
         <v>203</v>
       </c>
-      <c r="C38" s="57" t="s">
+      <c r="C38" s="42" t="s">
         <v>776</v>
       </c>
-      <c r="D38" s="57" t="s">
+      <c r="D38" s="42" t="s">
         <v>777</v>
       </c>
-      <c r="E38" s="57" t="s">
+      <c r="E38" s="42" t="s">
         <v>776</v>
       </c>
-      <c r="F38" s="57" t="s">
+      <c r="F38" s="42" t="s">
         <v>778</v>
       </c>
-      <c r="G38" s="57" t="s">
+      <c r="G38" s="42" t="s">
         <v>779</v>
       </c>
-      <c r="H38" s="57" t="s">
+      <c r="H38" s="42" t="s">
         <v>780</v>
       </c>
-      <c r="I38" s="57" t="s">
+      <c r="I38" s="42" t="s">
         <v>781</v>
       </c>
-      <c r="J38" s="57" t="s">
+      <c r="J38" s="42" t="s">
         <v>782</v>
       </c>
-      <c r="K38" s="57" t="s">
+      <c r="K38" s="42" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="56" t="n">
         <v>20</v>
       </c>
       <c r="B39" s="56" t="s">
         <v>212</v>
       </c>
-      <c r="C39" s="57" t="s">
+      <c r="C39" s="42" t="s">
         <v>784</v>
       </c>
-      <c r="D39" s="57" t="s">
+      <c r="D39" s="42" t="s">
         <v>785</v>
       </c>
-      <c r="E39" s="57" t="s">
+      <c r="E39" s="42" t="s">
         <v>784</v>
       </c>
-      <c r="F39" s="57" t="s">
+      <c r="F39" s="42" t="s">
         <v>786</v>
       </c>
-      <c r="G39" s="57" t="s">
+      <c r="G39" s="42" t="s">
         <v>787</v>
       </c>
-      <c r="H39" s="57" t="s">
+      <c r="H39" s="42" t="s">
         <v>788</v>
       </c>
-      <c r="I39" s="57" t="s">
+      <c r="I39" s="42" t="s">
         <v>789</v>
       </c>
-      <c r="J39" s="57" t="s">
+      <c r="J39" s="42" t="s">
         <v>790</v>
       </c>
-      <c r="K39" s="57" t="s">
+      <c r="K39" s="42" t="s">
         <v>791</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="58"/>
-      <c r="B40" s="58"/>
-      <c r="C40" s="58"/>
-      <c r="D40" s="58"/>
-      <c r="E40" s="58"/>
-      <c r="F40" s="58"/>
-      <c r="G40" s="58"/>
-      <c r="H40" s="58"/>
-      <c r="I40" s="58"/>
-      <c r="J40" s="59"/>
+      <c r="A40" s="57"/>
+      <c r="B40" s="57"/>
+      <c r="C40" s="57"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="58"/>
       <c r="K40" s="35"/>
     </row>
     <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="58"/>
-      <c r="B41" s="58"/>
-      <c r="C41" s="58"/>
-      <c r="D41" s="58"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="58"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="59"/>
+      <c r="A41" s="57"/>
+      <c r="B41" s="57"/>
+      <c r="C41" s="57"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="57"/>
+      <c r="F41" s="57"/>
+      <c r="G41" s="57"/>
+      <c r="H41" s="57"/>
+      <c r="I41" s="57"/>
+      <c r="J41" s="58"/>
       <c r="K41" s="35"/>
     </row>
     <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="58"/>
-      <c r="B42" s="58"/>
-      <c r="C42" s="58"/>
-      <c r="D42" s="58"/>
-      <c r="E42" s="58"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="58"/>
-      <c r="H42" s="58"/>
-      <c r="I42" s="58"/>
-      <c r="J42" s="59"/>
+      <c r="A42" s="57"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="57"/>
+      <c r="H42" s="57"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="58"/>
       <c r="K42" s="35"/>
     </row>
     <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="58"/>
-      <c r="B43" s="58"/>
-      <c r="C43" s="58"/>
-      <c r="D43" s="58"/>
-      <c r="E43" s="58"/>
-      <c r="F43" s="58"/>
-      <c r="G43" s="58"/>
-      <c r="H43" s="58"/>
-      <c r="I43" s="58"/>
-      <c r="J43" s="59"/>
+      <c r="A43" s="57"/>
+      <c r="B43" s="57"/>
+      <c r="C43" s="57"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="57"/>
+      <c r="F43" s="57"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="57"/>
+      <c r="I43" s="57"/>
+      <c r="J43" s="58"/>
       <c r="K43" s="35"/>
     </row>
     <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="58"/>
-      <c r="B44" s="58"/>
-      <c r="C44" s="58"/>
-      <c r="D44" s="58"/>
-      <c r="E44" s="58"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="58"/>
-      <c r="H44" s="58"/>
-      <c r="I44" s="58"/>
-      <c r="J44" s="59"/>
+      <c r="A44" s="57"/>
+      <c r="B44" s="57"/>
+      <c r="C44" s="57"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="57"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="57"/>
+      <c r="J44" s="58"/>
       <c r="K44" s="35"/>
     </row>
     <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="58"/>
-      <c r="B45" s="58"/>
-      <c r="C45" s="58"/>
-      <c r="D45" s="58"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="58"/>
-      <c r="H45" s="58"/>
-      <c r="I45" s="58"/>
-      <c r="J45" s="59"/>
+      <c r="A45" s="57"/>
+      <c r="B45" s="57"/>
+      <c r="C45" s="57"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="57"/>
+      <c r="J45" s="58"/>
       <c r="K45" s="35"/>
     </row>
     <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="58"/>
-      <c r="B46" s="58"/>
-      <c r="C46" s="58"/>
-      <c r="D46" s="58"/>
-      <c r="E46" s="58"/>
-      <c r="F46" s="58"/>
-      <c r="G46" s="58"/>
-      <c r="H46" s="58"/>
-      <c r="I46" s="58"/>
-      <c r="J46" s="59"/>
+      <c r="A46" s="57"/>
+      <c r="B46" s="57"/>
+      <c r="C46" s="57"/>
+      <c r="D46" s="57"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="57"/>
+      <c r="G46" s="57"/>
+      <c r="H46" s="57"/>
+      <c r="I46" s="57"/>
+      <c r="J46" s="58"/>
       <c r="K46" s="35"/>
     </row>
     <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="58"/>
-      <c r="B47" s="58"/>
-      <c r="C47" s="58"/>
-      <c r="D47" s="58"/>
-      <c r="E47" s="58"/>
-      <c r="F47" s="58"/>
-      <c r="G47" s="58"/>
-      <c r="H47" s="58"/>
-      <c r="I47" s="58"/>
-      <c r="J47" s="59"/>
+      <c r="A47" s="57"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="57"/>
+      <c r="G47" s="57"/>
+      <c r="H47" s="57"/>
+      <c r="I47" s="57"/>
+      <c r="J47" s="58"/>
       <c r="K47" s="35"/>
     </row>
     <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="58"/>
-      <c r="B48" s="58"/>
-      <c r="C48" s="58"/>
-      <c r="D48" s="58"/>
-      <c r="E48" s="58"/>
-      <c r="F48" s="58"/>
-      <c r="G48" s="58"/>
-      <c r="H48" s="58"/>
-      <c r="I48" s="58"/>
-      <c r="J48" s="59"/>
+      <c r="A48" s="57"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="57"/>
+      <c r="D48" s="57"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="57"/>
+      <c r="G48" s="57"/>
+      <c r="H48" s="57"/>
+      <c r="I48" s="57"/>
+      <c r="J48" s="58"/>
       <c r="K48" s="35"/>
     </row>
     <row r="49" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12689,7 +12685,7 @@
       <c r="I56" s="42"/>
       <c r="K56" s="35"/>
     </row>
-    <row r="57" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="54" t="s">
         <v>91</v>
       </c>
@@ -12731,31 +12727,31 @@
       <c r="B58" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="C58" s="57" t="s">
+      <c r="C58" s="42" t="s">
         <v>792</v>
       </c>
-      <c r="D58" s="57" t="s">
+      <c r="D58" s="42" t="s">
         <v>793</v>
       </c>
-      <c r="E58" s="57" t="s">
+      <c r="E58" s="42" t="s">
         <v>792</v>
       </c>
-      <c r="F58" s="57" t="s">
+      <c r="F58" s="42" t="s">
         <v>794</v>
       </c>
-      <c r="G58" s="57" t="s">
+      <c r="G58" s="42" t="s">
         <v>795</v>
       </c>
-      <c r="H58" s="57" t="s">
+      <c r="H58" s="42" t="s">
         <v>796</v>
       </c>
-      <c r="I58" s="57" t="s">
+      <c r="I58" s="42" t="s">
         <v>797</v>
       </c>
-      <c r="J58" s="57" t="s">
+      <c r="J58" s="42" t="s">
         <v>798</v>
       </c>
-      <c r="K58" s="57" t="s">
+      <c r="K58" s="42" t="s">
         <v>799</v>
       </c>
     </row>
@@ -12766,31 +12762,31 @@
       <c r="B59" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="C59" s="57" t="s">
+      <c r="C59" s="42" t="s">
         <v>800</v>
       </c>
-      <c r="D59" s="57" t="s">
+      <c r="D59" s="42" t="s">
         <v>801</v>
       </c>
-      <c r="E59" s="57" t="s">
+      <c r="E59" s="42" t="s">
         <v>800</v>
       </c>
-      <c r="F59" s="57" t="s">
+      <c r="F59" s="42" t="s">
         <v>802</v>
       </c>
-      <c r="G59" s="57" t="s">
+      <c r="G59" s="42" t="s">
         <v>803</v>
       </c>
-      <c r="H59" s="57" t="s">
+      <c r="H59" s="42" t="s">
         <v>804</v>
       </c>
-      <c r="I59" s="57" t="s">
+      <c r="I59" s="42" t="s">
         <v>805</v>
       </c>
-      <c r="J59" s="57" t="s">
+      <c r="J59" s="42" t="s">
         <v>806</v>
       </c>
-      <c r="K59" s="57" t="s">
+      <c r="K59" s="42" t="s">
         <v>807</v>
       </c>
     </row>
@@ -12801,31 +12797,31 @@
       <c r="B60" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="C60" s="57" t="s">
+      <c r="C60" s="42" t="s">
         <v>808</v>
       </c>
-      <c r="D60" s="57" t="s">
+      <c r="D60" s="42" t="s">
         <v>809</v>
       </c>
-      <c r="E60" s="57" t="s">
+      <c r="E60" s="42" t="s">
         <v>808</v>
       </c>
-      <c r="F60" s="57" t="s">
+      <c r="F60" s="42" t="s">
         <v>810</v>
       </c>
-      <c r="G60" s="57" t="s">
+      <c r="G60" s="42" t="s">
         <v>811</v>
       </c>
-      <c r="H60" s="57" t="s">
+      <c r="H60" s="42" t="s">
         <v>812</v>
       </c>
-      <c r="I60" s="57" t="s">
+      <c r="I60" s="42" t="s">
         <v>813</v>
       </c>
-      <c r="J60" s="57" t="s">
+      <c r="J60" s="42" t="s">
         <v>513</v>
       </c>
-      <c r="K60" s="57" t="s">
+      <c r="K60" s="42" t="s">
         <v>814</v>
       </c>
     </row>
@@ -12836,66 +12832,66 @@
       <c r="B61" s="56" t="s">
         <v>129</v>
       </c>
-      <c r="C61" s="57" t="s">
+      <c r="C61" s="42" t="s">
         <v>815</v>
       </c>
-      <c r="D61" s="57" t="s">
+      <c r="D61" s="42" t="s">
         <v>816</v>
       </c>
-      <c r="E61" s="57" t="s">
+      <c r="E61" s="42" t="s">
         <v>815</v>
       </c>
-      <c r="F61" s="57" t="s">
+      <c r="F61" s="42" t="s">
         <v>817</v>
       </c>
-      <c r="G61" s="57" t="s">
+      <c r="G61" s="42" t="s">
         <v>818</v>
       </c>
-      <c r="H61" s="57" t="s">
+      <c r="H61" s="42" t="s">
         <v>819</v>
       </c>
-      <c r="I61" s="57" t="s">
+      <c r="I61" s="42" t="s">
         <v>820</v>
       </c>
-      <c r="J61" s="57" t="s">
+      <c r="J61" s="42" t="s">
         <v>821</v>
       </c>
-      <c r="K61" s="57" t="s">
+      <c r="K61" s="42" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="56" t="n">
         <v>6</v>
       </c>
       <c r="B62" s="56" t="s">
         <v>136</v>
       </c>
-      <c r="C62" s="57" t="s">
+      <c r="C62" s="42" t="s">
         <v>823</v>
       </c>
-      <c r="D62" s="57" t="s">
+      <c r="D62" s="42" t="s">
         <v>824</v>
       </c>
-      <c r="E62" s="57" t="s">
+      <c r="E62" s="42" t="s">
         <v>823</v>
       </c>
-      <c r="F62" s="57" t="s">
+      <c r="F62" s="42" t="s">
         <v>825</v>
       </c>
-      <c r="G62" s="57" t="s">
+      <c r="G62" s="42" t="s">
         <v>826</v>
       </c>
-      <c r="H62" s="57" t="s">
+      <c r="H62" s="42" t="s">
         <v>827</v>
       </c>
-      <c r="I62" s="57" t="s">
+      <c r="I62" s="42" t="s">
         <v>828</v>
       </c>
-      <c r="J62" s="57" t="s">
+      <c r="J62" s="42" t="s">
         <v>829</v>
       </c>
-      <c r="K62" s="57" t="s">
+      <c r="K62" s="42" t="s">
         <v>830</v>
       </c>
     </row>
@@ -12906,31 +12902,31 @@
       <c r="B63" s="56" t="s">
         <v>142</v>
       </c>
-      <c r="C63" s="57" t="s">
+      <c r="C63" s="42" t="s">
         <v>831</v>
       </c>
-      <c r="D63" s="57" t="s">
+      <c r="D63" s="42" t="s">
         <v>832</v>
       </c>
-      <c r="E63" s="57" t="s">
+      <c r="E63" s="42" t="s">
         <v>831</v>
       </c>
-      <c r="F63" s="57" t="s">
+      <c r="F63" s="42" t="s">
         <v>833</v>
       </c>
-      <c r="G63" s="57" t="s">
+      <c r="G63" s="42" t="s">
         <v>834</v>
       </c>
-      <c r="H63" s="57" t="s">
+      <c r="H63" s="42" t="s">
         <v>835</v>
       </c>
-      <c r="I63" s="57" t="s">
+      <c r="I63" s="42" t="s">
         <v>836</v>
       </c>
-      <c r="J63" s="57" t="s">
+      <c r="J63" s="42" t="s">
         <v>837</v>
       </c>
-      <c r="K63" s="57" t="s">
+      <c r="K63" s="42" t="s">
         <v>838</v>
       </c>
     </row>
@@ -12941,66 +12937,66 @@
       <c r="B64" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="C64" s="57" t="s">
+      <c r="C64" s="42" t="s">
         <v>839</v>
       </c>
-      <c r="D64" s="57" t="s">
+      <c r="D64" s="42" t="s">
         <v>840</v>
       </c>
-      <c r="E64" s="57" t="s">
+      <c r="E64" s="42" t="s">
         <v>839</v>
       </c>
-      <c r="F64" s="57" t="s">
+      <c r="F64" s="42" t="s">
         <v>841</v>
       </c>
-      <c r="G64" s="57" t="s">
+      <c r="G64" s="42" t="s">
         <v>842</v>
       </c>
-      <c r="H64" s="57" t="s">
+      <c r="H64" s="42" t="s">
         <v>843</v>
       </c>
-      <c r="I64" s="57" t="s">
+      <c r="I64" s="42" t="s">
         <v>844</v>
       </c>
-      <c r="J64" s="57" t="s">
+      <c r="J64" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="K64" s="57" t="s">
+      <c r="K64" s="42" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="56" t="n">
         <v>10</v>
       </c>
       <c r="B65" s="56" t="s">
         <v>154</v>
       </c>
-      <c r="C65" s="57" t="s">
+      <c r="C65" s="42" t="s">
         <v>847</v>
       </c>
-      <c r="D65" s="57" t="s">
+      <c r="D65" s="42" t="s">
         <v>848</v>
       </c>
-      <c r="E65" s="57" t="s">
+      <c r="E65" s="42" t="s">
         <v>847</v>
       </c>
-      <c r="F65" s="57" t="s">
+      <c r="F65" s="42" t="s">
         <v>849</v>
       </c>
-      <c r="G65" s="57" t="s">
+      <c r="G65" s="42" t="s">
         <v>850</v>
       </c>
-      <c r="H65" s="57" t="s">
+      <c r="H65" s="42" t="s">
         <v>851</v>
       </c>
-      <c r="I65" s="57" t="s">
+      <c r="I65" s="42" t="s">
         <v>852</v>
       </c>
-      <c r="J65" s="57" t="s">
+      <c r="J65" s="42" t="s">
         <v>853</v>
       </c>
-      <c r="K65" s="57" t="s">
+      <c r="K65" s="42" t="s">
         <v>854</v>
       </c>
     </row>
@@ -13011,31 +13007,31 @@
       <c r="B66" s="56" t="s">
         <v>161</v>
       </c>
-      <c r="C66" s="57" t="s">
+      <c r="C66" s="42" t="s">
         <v>855</v>
       </c>
-      <c r="D66" s="57" t="s">
+      <c r="D66" s="42" t="s">
         <v>856</v>
       </c>
-      <c r="E66" s="57" t="s">
+      <c r="E66" s="42" t="s">
         <v>855</v>
       </c>
-      <c r="F66" s="57" t="s">
+      <c r="F66" s="42" t="s">
         <v>857</v>
       </c>
-      <c r="G66" s="57" t="s">
+      <c r="G66" s="42" t="s">
         <v>858</v>
       </c>
-      <c r="H66" s="57" t="s">
+      <c r="H66" s="42" t="s">
         <v>859</v>
       </c>
-      <c r="I66" s="57" t="s">
+      <c r="I66" s="42" t="s">
         <v>860</v>
       </c>
-      <c r="J66" s="57" t="s">
+      <c r="J66" s="42" t="s">
         <v>861</v>
       </c>
-      <c r="K66" s="57" t="s">
+      <c r="K66" s="42" t="s">
         <v>862</v>
       </c>
     </row>
@@ -13046,206 +13042,206 @@
       <c r="B67" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="C67" s="57" t="s">
+      <c r="C67" s="42" t="s">
         <v>863</v>
       </c>
-      <c r="D67" s="57" t="s">
+      <c r="D67" s="42" t="s">
         <v>864</v>
       </c>
-      <c r="E67" s="57" t="s">
+      <c r="E67" s="42" t="s">
         <v>863</v>
       </c>
-      <c r="F67" s="57" t="s">
+      <c r="F67" s="42" t="s">
         <v>865</v>
       </c>
-      <c r="G67" s="57" t="s">
+      <c r="G67" s="42" t="s">
         <v>866</v>
       </c>
-      <c r="H67" s="57" t="s">
+      <c r="H67" s="42" t="s">
         <v>867</v>
       </c>
-      <c r="I67" s="57" t="s">
+      <c r="I67" s="42" t="s">
         <v>868</v>
       </c>
-      <c r="J67" s="57" t="s">
+      <c r="J67" s="42" t="s">
         <v>869</v>
       </c>
-      <c r="K67" s="57" t="s">
+      <c r="K67" s="42" t="s">
         <v>870</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="56" t="n">
         <v>14</v>
       </c>
       <c r="B68" s="56" t="s">
         <v>176</v>
       </c>
-      <c r="C68" s="57" t="s">
+      <c r="C68" s="42" t="s">
         <v>871</v>
       </c>
-      <c r="D68" s="57" t="s">
+      <c r="D68" s="42" t="s">
         <v>872</v>
       </c>
-      <c r="E68" s="57" t="s">
+      <c r="E68" s="42" t="s">
         <v>871</v>
       </c>
-      <c r="F68" s="57" t="s">
+      <c r="F68" s="42" t="s">
         <v>873</v>
       </c>
-      <c r="G68" s="57" t="s">
+      <c r="G68" s="42" t="s">
         <v>874</v>
       </c>
-      <c r="H68" s="57" t="s">
+      <c r="H68" s="42" t="s">
         <v>875</v>
       </c>
-      <c r="I68" s="57" t="s">
+      <c r="I68" s="42" t="s">
         <v>876</v>
       </c>
-      <c r="J68" s="57" t="s">
+      <c r="J68" s="42" t="s">
         <v>877</v>
       </c>
-      <c r="K68" s="57" t="s">
+      <c r="K68" s="42" t="s">
         <v>878</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="56" t="n">
         <v>16</v>
       </c>
       <c r="B69" s="56" t="s">
         <v>185</v>
       </c>
-      <c r="C69" s="57" t="s">
+      <c r="C69" s="42" t="s">
         <v>879</v>
       </c>
-      <c r="D69" s="57" t="s">
+      <c r="D69" s="42" t="s">
         <v>880</v>
       </c>
-      <c r="E69" s="57" t="s">
+      <c r="E69" s="42" t="s">
         <v>879</v>
       </c>
-      <c r="F69" s="57" t="s">
+      <c r="F69" s="42" t="s">
         <v>881</v>
       </c>
-      <c r="G69" s="57" t="s">
+      <c r="G69" s="42" t="s">
         <v>882</v>
       </c>
-      <c r="H69" s="57" t="s">
+      <c r="H69" s="42" t="s">
         <v>883</v>
       </c>
-      <c r="I69" s="57" t="s">
+      <c r="I69" s="42" t="s">
         <v>884</v>
       </c>
-      <c r="J69" s="57" t="s">
+      <c r="J69" s="42" t="s">
         <v>885</v>
       </c>
-      <c r="K69" s="57" t="s">
+      <c r="K69" s="42" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="56" t="n">
         <v>17</v>
       </c>
       <c r="B70" s="56" t="s">
         <v>194</v>
       </c>
-      <c r="C70" s="57" t="s">
+      <c r="C70" s="42" t="s">
         <v>887</v>
       </c>
-      <c r="D70" s="57" t="s">
+      <c r="D70" s="42" t="s">
         <v>888</v>
       </c>
-      <c r="E70" s="57" t="s">
+      <c r="E70" s="42" t="s">
         <v>887</v>
       </c>
-      <c r="F70" s="57" t="s">
+      <c r="F70" s="42" t="s">
         <v>889</v>
       </c>
-      <c r="G70" s="57" t="s">
+      <c r="G70" s="42" t="s">
         <v>890</v>
       </c>
-      <c r="H70" s="57" t="s">
+      <c r="H70" s="42" t="s">
         <v>891</v>
       </c>
-      <c r="I70" s="57" t="s">
+      <c r="I70" s="42" t="s">
         <v>892</v>
       </c>
-      <c r="J70" s="57" t="s">
+      <c r="J70" s="42" t="s">
         <v>893</v>
       </c>
-      <c r="K70" s="57" t="s">
+      <c r="K70" s="42" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="56" t="n">
         <v>18</v>
       </c>
       <c r="B71" s="56" t="s">
         <v>203</v>
       </c>
-      <c r="C71" s="57" t="s">
+      <c r="C71" s="42" t="s">
         <v>895</v>
       </c>
-      <c r="D71" s="57" t="s">
+      <c r="D71" s="42" t="s">
         <v>896</v>
       </c>
-      <c r="E71" s="57" t="s">
+      <c r="E71" s="42" t="s">
         <v>895</v>
       </c>
-      <c r="F71" s="57" t="s">
+      <c r="F71" s="42" t="s">
         <v>897</v>
       </c>
-      <c r="G71" s="57" t="s">
+      <c r="G71" s="42" t="s">
         <v>898</v>
       </c>
-      <c r="H71" s="57" t="s">
+      <c r="H71" s="42" t="s">
         <v>899</v>
       </c>
-      <c r="I71" s="57" t="s">
+      <c r="I71" s="42" t="s">
         <v>900</v>
       </c>
-      <c r="J71" s="57" t="s">
+      <c r="J71" s="42" t="s">
         <v>901</v>
       </c>
-      <c r="K71" s="57" t="s">
+      <c r="K71" s="42" t="s">
         <v>902</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="56" t="n">
         <v>20</v>
       </c>
       <c r="B72" s="56" t="s">
         <v>212</v>
       </c>
-      <c r="C72" s="57" t="s">
+      <c r="C72" s="42" t="s">
         <v>903</v>
       </c>
-      <c r="D72" s="57" t="s">
+      <c r="D72" s="42" t="s">
         <v>904</v>
       </c>
-      <c r="E72" s="57" t="s">
+      <c r="E72" s="42" t="s">
         <v>903</v>
       </c>
-      <c r="F72" s="57" t="s">
+      <c r="F72" s="42" t="s">
         <v>905</v>
       </c>
-      <c r="G72" s="57" t="s">
+      <c r="G72" s="42" t="s">
         <v>906</v>
       </c>
-      <c r="H72" s="57" t="s">
+      <c r="H72" s="42" t="s">
         <v>907</v>
       </c>
-      <c r="I72" s="57" t="s">
+      <c r="I72" s="42" t="s">
         <v>908</v>
       </c>
-      <c r="J72" s="57" t="s">
+      <c r="J72" s="42" t="s">
         <v>909</v>
       </c>
-      <c r="K72" s="57" t="s">
+      <c r="K72" s="42" t="s">
         <v>910</v>
       </c>
     </row>
